--- a/fracas/fracas_worksheet.xlsx
+++ b/fracas/fracas_worksheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ivorm\yarn2fol\fracas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5554A501-EBDA-4844-94E3-BA0052A5011B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37116522-A98F-4D1D-8187-72A533ED3E89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34440" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{DDDA1AFE-174D-47B1-8070-326023C11386}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{DDDA1AFE-174D-47B1-8070-326023C11386}"/>
   </bookViews>
   <sheets>
     <sheet name="fracas" sheetId="1" r:id="rId1"/>
@@ -19,11 +19,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">fracas!$A$1:$M$347</definedName>
   </definedNames>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2372" uniqueCount="734">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2374" uniqueCount="738">
   <si>
     <t>section</t>
   </si>
@@ -1645,9 +1646,6 @@
     <t>Smith wrote it in 1992.</t>
   </si>
   <si>
-    <t>anaphora</t>
-  </si>
-  <si>
     <t>Smith wrote a novel in 1992.</t>
   </si>
   <si>
@@ -2116,9 +2114,6 @@
     <t>tad-1</t>
   </si>
   <si>
-    <t>how to model empty temp layer</t>
-  </si>
-  <si>
     <t>tad-skip</t>
   </si>
   <si>
@@ -2146,66 +2141,18 @@
     <t>shared node might not work? Check</t>
   </si>
   <si>
-    <t>empty temp as L edge but could be H</t>
-  </si>
-  <si>
-    <t>perfective, overlaps=total_overlap for perfective might be useful, or just shift 1992 to the winning</t>
-  </si>
-  <si>
     <t>negated true - need axiom</t>
   </si>
   <si>
     <t>need axiom</t>
   </si>
   <si>
-    <t>axiom? Definitely time linearity axiom</t>
-  </si>
-  <si>
     <t>C edge with and</t>
   </si>
   <si>
     <t>xor?</t>
   </si>
   <si>
-    <t>premise is perfective with two events marked by BEFORE and temp, hypothesis is endeavor with duration</t>
-  </si>
-  <si>
-    <t>premise is perfective with two events marked by BEFORE and temp</t>
-  </si>
-  <si>
-    <t>≥1 and ≥2</t>
-  </si>
-  <si>
-    <t>1 and ≥2</t>
-  </si>
-  <si>
-    <t>same as above: duration+endeavor?</t>
-  </si>
-  <si>
-    <t>tad_skip</t>
-  </si>
-  <si>
-    <t>duration+endeavor</t>
-  </si>
-  <si>
-    <t>just annotate as duration+endeavor? Not sure if I can do the succession of perfective events: just see them as a continuous endeavor…; hypothesis is the same annotation?</t>
-  </si>
-  <si>
-    <t>before + progressive, h: just past for run</t>
-  </si>
-  <si>
-    <t>before + state; chain_of_businesses as a node</t>
-  </si>
-  <si>
-    <t>chose endeavor cause it is easier</t>
-  </si>
-  <si>
-    <t>premise: endeavor and perfective annotated with BEFORE</t>
-  </si>
-  <si>
-    <t>enforce perfective reading; perfective means finished axiom?</t>
-  </si>
-  <si>
     <t>non-intersectional adjective - represent former as past habitual instead; axiom?</t>
   </si>
   <si>
@@ -2225,6 +2172,72 @@
   </si>
   <si>
     <t>non-intersectional adjective; successful on John with mod,  not sure if correct</t>
+  </si>
+  <si>
+    <t>found =&gt; exists AXIOM</t>
+  </si>
+  <si>
+    <t>accomplishment+temp</t>
+  </si>
+  <si>
+    <t>accomplishment+temp; anaphora</t>
+  </si>
+  <si>
+    <t>achievement+temp; anaphora</t>
+  </si>
+  <si>
+    <t>accomplishment+duration (hypothesis could be interpreted as endeavor)</t>
+  </si>
+  <si>
+    <t>accomplishment+duration</t>
+  </si>
+  <si>
+    <t>p: achievement+before; h: accomplishment+duration (AXIOM!!)</t>
+  </si>
+  <si>
+    <t>achievement+before</t>
+  </si>
+  <si>
+    <t>accomplishment+duration? Not sure if I can do the succession of perfective events…; hypothesis is the same annotation?</t>
+  </si>
+  <si>
+    <t>p: progressive+before, h: just past due to ambiguity</t>
+  </si>
+  <si>
+    <t>state+before; chain_of_businesses as a node</t>
+  </si>
+  <si>
+    <t>state+duration</t>
+  </si>
+  <si>
+    <t>state+duration; ≥1 and ≥2 (skolemization)</t>
+  </si>
+  <si>
+    <t>state+duration; 1 and ≥2 (skolemization)</t>
+  </si>
+  <si>
+    <t>endeavor+duration</t>
+  </si>
+  <si>
+    <t>endeavor+duration; ≥1 and ≥2 (skolemization)</t>
+  </si>
+  <si>
+    <t>endeavor+duration? Endeavor of successive accomplishments…</t>
+  </si>
+  <si>
+    <t>accomplishment+temp; accomplishment =&gt; finished (AXIOM)?</t>
+  </si>
+  <si>
+    <t>achievement+temp</t>
+  </si>
+  <si>
+    <t>state+duration; date-interval; 1988&lt;1990&lt;1992 (AXIOM)</t>
+  </si>
+  <si>
+    <t>know is extensional unlike want which is intensional</t>
+  </si>
+  <si>
+    <t>achievement+temp, overlaps=total_overlap for achievement might be useful, or just shift 1992 to the winning</t>
   </si>
 </sst>
 </file>
@@ -2367,7 +2380,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2565,6 +2578,30 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -2726,13 +2763,16 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3109,11 +3149,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{184E8DB1-1DA0-4161-AC11-ADA355556CCF}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:O347"/>
+  <dimension ref="A1:P347"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="8" max="8" width="31.90625" customWidth="1"/>
-    <col min="11" max="11" width="51.08984375" customWidth="1"/>
+    <col min="11" max="11" width="54.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.35">
@@ -3145,7 +3185,7 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="K1" t="s">
         <v>9</v>
@@ -3157,7 +3197,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -3184,7 +3224,7 @@
         <v>17</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>18</v>
@@ -3276,7 +3316,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -3305,7 +3345,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -3314,7 +3354,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -3343,7 +3383,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="L7">
         <v>1</v>
@@ -3352,7 +3392,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -3381,7 +3421,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="L8">
         <v>1</v>
@@ -3390,7 +3430,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -3419,7 +3459,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="L9">
         <v>1</v>
@@ -3428,7 +3468,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -3457,7 +3497,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="L10">
         <v>1</v>
@@ -3466,7 +3506,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -3495,7 +3535,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="L11">
         <v>1</v>
@@ -3617,7 +3657,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -3646,7 +3686,7 @@
         <v>1</v>
       </c>
       <c r="K16" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="L16">
         <v>1</v>
@@ -3690,7 +3730,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -3719,7 +3759,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="L18">
         <v>1</v>
@@ -3864,7 +3904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -3893,7 +3933,7 @@
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="L24">
         <v>1</v>
@@ -3902,7 +3942,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -3931,7 +3971,7 @@
         <v>1</v>
       </c>
       <c r="K25" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="L25">
         <v>1</v>
@@ -3940,7 +3980,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>12</v>
       </c>
@@ -3969,7 +4009,7 @@
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="L26">
         <v>1</v>
@@ -4056,7 +4096,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>12</v>
       </c>
@@ -4085,7 +4125,7 @@
         <v>1</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="L30">
         <v>1</v>
@@ -4126,7 +4166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>12</v>
       </c>
@@ -4155,7 +4195,7 @@
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="L32">
         <v>1</v>
@@ -4329,7 +4369,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>12</v>
       </c>
@@ -4358,7 +4398,7 @@
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="L39">
         <v>1</v>
@@ -4555,7 +4595,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>12</v>
       </c>
@@ -4584,7 +4624,7 @@
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="L47">
         <v>2</v>
@@ -4619,7 +4659,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>12</v>
       </c>
@@ -4648,7 +4688,7 @@
         <v>1</v>
       </c>
       <c r="K49" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="L49">
         <v>1</v>
@@ -4813,7 +4853,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>12</v>
       </c>
@@ -4874,7 +4914,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>12</v>
       </c>
@@ -4935,7 +4975,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>12</v>
       </c>
@@ -4961,10 +5001,10 @@
         <v>17</v>
       </c>
       <c r="J60" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="K60" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="M60" t="s">
         <v>55</v>
@@ -5054,7 +5094,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>12</v>
       </c>
@@ -5083,7 +5123,7 @@
         <v>1</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="L64">
         <v>1</v>
@@ -5248,7 +5288,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>12</v>
       </c>
@@ -5413,7 +5453,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>12</v>
       </c>
@@ -5532,7 +5572,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>12</v>
       </c>
@@ -5567,7 +5607,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>163</v>
       </c>
@@ -5602,7 +5642,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>163</v>
       </c>
@@ -5663,7 +5703,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>163</v>
       </c>
@@ -5692,7 +5732,7 @@
         <v>1</v>
       </c>
       <c r="K85" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="L85">
         <v>1</v>
@@ -5701,7 +5741,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>163</v>
       </c>
@@ -5730,7 +5770,7 @@
         <v>1</v>
       </c>
       <c r="K86" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="L86">
         <v>1</v>
@@ -5739,7 +5779,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>163</v>
       </c>
@@ -5768,7 +5808,7 @@
         <v>1</v>
       </c>
       <c r="K87" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="L87">
         <v>1</v>
@@ -5777,7 +5817,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>163</v>
       </c>
@@ -5809,7 +5849,7 @@
         <v>1</v>
       </c>
       <c r="K88" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="L88">
         <v>1</v>
@@ -5847,7 +5887,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>163</v>
       </c>
@@ -5876,7 +5916,7 @@
         <v>1</v>
       </c>
       <c r="K90" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="L90">
         <v>1</v>
@@ -5885,41 +5925,41 @@
         <v>82</v>
       </c>
     </row>
-    <row r="91" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="5" t="s">
+    <row r="91" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
         <v>163</v>
       </c>
-      <c r="B91" s="5" t="s">
+      <c r="B91" t="s">
         <v>180</v>
       </c>
-      <c r="C91" s="5">
+      <c r="C91">
         <v>90</v>
       </c>
-      <c r="D91" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F91" s="5">
-        <v>0</v>
-      </c>
-      <c r="G91" s="5" t="s">
+      <c r="D91" t="s">
+        <v>14</v>
+      </c>
+      <c r="F91">
+        <v>0</v>
+      </c>
+      <c r="G91" t="s">
         <v>181</v>
       </c>
-      <c r="H91" s="5" t="s">
+      <c r="H91" t="s">
         <v>182</v>
       </c>
-      <c r="I91" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J91" s="5">
-        <v>1</v>
-      </c>
-      <c r="K91" s="5" t="s">
-        <v>704</v>
-      </c>
-      <c r="L91" s="5">
-        <v>1</v>
-      </c>
-      <c r="M91" s="5" t="s">
+      <c r="I91" t="s">
+        <v>17</v>
+      </c>
+      <c r="J91">
+        <v>1</v>
+      </c>
+      <c r="K91" t="s">
+        <v>702</v>
+      </c>
+      <c r="L91">
+        <v>1</v>
+      </c>
+      <c r="M91" t="s">
         <v>27</v>
       </c>
     </row>
@@ -5949,7 +5989,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>163</v>
       </c>
@@ -5978,7 +6018,7 @@
         <v>1</v>
       </c>
       <c r="K93" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="L93">
         <v>1</v>
@@ -5987,7 +6027,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>163</v>
       </c>
@@ -6016,7 +6056,7 @@
         <v>1</v>
       </c>
       <c r="K94" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="L94">
         <v>1</v>
@@ -6077,7 +6117,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>163</v>
       </c>
@@ -6106,7 +6146,7 @@
         <v>1</v>
       </c>
       <c r="K97" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="L97">
         <v>1</v>
@@ -6115,45 +6155,48 @@
         <v>27</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A98" t="s">
+    <row r="98" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="C98">
+      <c r="C98" s="3">
         <v>97</v>
       </c>
-      <c r="D98" t="s">
-        <v>14</v>
-      </c>
-      <c r="F98">
-        <v>0</v>
-      </c>
-      <c r="G98" t="s">
+      <c r="D98" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3">
+        <v>0</v>
+      </c>
+      <c r="G98" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="H98" t="s">
+      <c r="H98" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="I98" t="s">
-        <v>17</v>
-      </c>
-      <c r="J98">
-        <v>1</v>
-      </c>
-      <c r="K98" t="s">
-        <v>730</v>
-      </c>
-      <c r="L98">
-        <v>1</v>
-      </c>
-      <c r="M98" t="s">
+      <c r="I98" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J98" s="3">
+        <v>1</v>
+      </c>
+      <c r="K98" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="L98" s="3">
+        <v>1</v>
+      </c>
+      <c r="M98" s="3" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="99" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+      <c r="N98" s="3"/>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>163</v>
       </c>
@@ -6179,7 +6222,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="100" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>163</v>
       </c>
@@ -6205,45 +6248,48 @@
         <v>17</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A101" t="s">
+    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="C101">
+      <c r="C101" s="3">
         <v>100</v>
       </c>
-      <c r="D101" t="s">
-        <v>14</v>
-      </c>
-      <c r="F101">
-        <v>0</v>
-      </c>
-      <c r="G101" t="s">
+      <c r="D101" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="H101" t="s">
+      <c r="H101" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="I101" t="s">
-        <v>17</v>
-      </c>
-      <c r="J101">
-        <v>1</v>
-      </c>
-      <c r="K101" t="s">
-        <v>731</v>
-      </c>
-      <c r="L101">
-        <v>1</v>
-      </c>
-      <c r="M101" t="s">
+      <c r="I101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J101" s="3">
+        <v>1</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="L101" s="3">
+        <v>1</v>
+      </c>
+      <c r="M101" s="3" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="102" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+      <c r="N101" s="3"/>
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>163</v>
       </c>
@@ -6269,7 +6315,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="103" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>163</v>
       </c>
@@ -6295,7 +6341,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="104" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>163</v>
       </c>
@@ -6321,7 +6367,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="105" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>163</v>
       </c>
@@ -6347,7 +6393,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>163</v>
       </c>
@@ -6376,7 +6422,7 @@
         <v>1</v>
       </c>
       <c r="K106" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="L106">
         <v>1</v>
@@ -6385,7 +6431,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>163</v>
       </c>
@@ -6420,7 +6466,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>163</v>
       </c>
@@ -6446,7 +6492,7 @@
         <v>17</v>
       </c>
       <c r="J108" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="K108" t="s">
         <v>213</v>
@@ -6458,7 +6504,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>163</v>
       </c>
@@ -6484,7 +6530,7 @@
         <v>17</v>
       </c>
       <c r="J109" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="K109" t="s">
         <v>213</v>
@@ -6496,7 +6542,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>163</v>
       </c>
@@ -6528,7 +6574,7 @@
         <v>1</v>
       </c>
       <c r="K110" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="L110">
         <v>1</v>
@@ -6537,7 +6583,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>163</v>
       </c>
@@ -6572,7 +6618,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="112" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>163</v>
       </c>
@@ -6656,7 +6702,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>223</v>
       </c>
@@ -6685,7 +6731,7 @@
         <v>1</v>
       </c>
       <c r="K115" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="L115">
         <v>1</v>
@@ -6694,7 +6740,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>223</v>
       </c>
@@ -6723,7 +6769,7 @@
         <v>1</v>
       </c>
       <c r="K116" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L116">
         <v>1</v>
@@ -6732,7 +6778,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>223</v>
       </c>
@@ -6761,7 +6807,7 @@
         <v>1</v>
       </c>
       <c r="K117" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="L117">
         <v>1</v>
@@ -7351,7 +7397,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>223</v>
       </c>
@@ -7389,7 +7435,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>223</v>
       </c>
@@ -7418,7 +7464,7 @@
         <v>1</v>
       </c>
       <c r="K141" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="L141">
         <v>1</v>
@@ -7661,7 +7707,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>279</v>
       </c>
@@ -7690,7 +7736,7 @@
         <v>1</v>
       </c>
       <c r="K151" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="L151">
         <v>1</v>
@@ -7699,7 +7745,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>279</v>
       </c>
@@ -7728,7 +7774,7 @@
         <v>1</v>
       </c>
       <c r="K152" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="L152">
         <v>1</v>
@@ -7737,7 +7783,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>279</v>
       </c>
@@ -7766,7 +7812,7 @@
         <v>1</v>
       </c>
       <c r="K153" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="L153">
         <v>1</v>
@@ -7775,7 +7821,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>279</v>
       </c>
@@ -7804,7 +7850,7 @@
         <v>1</v>
       </c>
       <c r="K154" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="L154">
         <v>1</v>
@@ -8209,7 +8255,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>279</v>
       </c>
@@ -8241,7 +8287,7 @@
         <v>1</v>
       </c>
       <c r="K170" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="L170">
         <v>1</v>
@@ -8250,7 +8296,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>279</v>
       </c>
@@ -8282,7 +8328,7 @@
         <v>1</v>
       </c>
       <c r="K171" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="L171">
         <v>1</v>
@@ -8317,7 +8363,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>279</v>
       </c>
@@ -8343,7 +8389,7 @@
         <v>17</v>
       </c>
       <c r="J173" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="K173" t="s">
         <v>340</v>
@@ -8407,7 +8453,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>279</v>
       </c>
@@ -8439,7 +8485,7 @@
         <v>1</v>
       </c>
       <c r="K176" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="L176">
         <v>1</v>
@@ -8448,7 +8494,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>279</v>
       </c>
@@ -8480,7 +8526,7 @@
         <v>1</v>
       </c>
       <c r="K177" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="L177">
         <v>1</v>
@@ -8515,7 +8561,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>279</v>
       </c>
@@ -8544,7 +8590,7 @@
         <v>1</v>
       </c>
       <c r="K179" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="L179">
         <v>1</v>
@@ -8579,7 +8625,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
         <v>279</v>
       </c>
@@ -8609,7 +8655,7 @@
         <v>1</v>
       </c>
       <c r="K181" s="2" t="s">
-        <v>732</v>
+        <v>714</v>
       </c>
       <c r="L181" s="2">
         <v>1</v>
@@ -8646,7 +8692,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>279</v>
       </c>
@@ -8684,7 +8730,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>279</v>
       </c>
@@ -8716,7 +8762,7 @@
         <v>1</v>
       </c>
       <c r="K184" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="L184">
         <v>1</v>
@@ -8751,7 +8797,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>279</v>
       </c>
@@ -8789,7 +8835,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>279</v>
       </c>
@@ -8821,7 +8867,7 @@
         <v>1</v>
       </c>
       <c r="K187" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="L187">
         <v>1</v>
@@ -8830,7 +8876,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>279</v>
       </c>
@@ -8952,7 +8998,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>279</v>
       </c>
@@ -8978,7 +9024,7 @@
         <v>17</v>
       </c>
       <c r="J192" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="K192" t="s">
         <v>340</v>
@@ -9016,7 +9062,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>279</v>
       </c>
@@ -9042,7 +9088,7 @@
         <v>17</v>
       </c>
       <c r="J194" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="K194" t="s">
         <v>340</v>
@@ -9080,7 +9126,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>279</v>
       </c>
@@ -9106,7 +9152,7 @@
         <v>17</v>
       </c>
       <c r="J196" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="K196" t="s">
         <v>340</v>
@@ -9144,7 +9190,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>386</v>
       </c>
@@ -9179,7 +9225,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>386</v>
       </c>
@@ -9211,7 +9257,7 @@
         <v>1</v>
       </c>
       <c r="K199" t="s">
-        <v>727</v>
+        <v>709</v>
       </c>
       <c r="L199">
         <v>2</v>
@@ -9220,7 +9266,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>386</v>
       </c>
@@ -9252,7 +9298,7 @@
         <v>1</v>
       </c>
       <c r="K200" t="s">
-        <v>733</v>
+        <v>715</v>
       </c>
       <c r="L200">
         <v>2</v>
@@ -9313,7 +9359,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>386</v>
       </c>
@@ -9348,7 +9394,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>386</v>
       </c>
@@ -9383,7 +9429,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>386</v>
       </c>
@@ -9421,7 +9467,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>386</v>
       </c>
@@ -9722,7 +9768,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" s="3" t="s">
         <v>386</v>
       </c>
@@ -9749,7 +9795,7 @@
         <v>17</v>
       </c>
       <c r="J217" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="K217" s="3"/>
       <c r="L217" s="3">
@@ -9787,7 +9833,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>386</v>
       </c>
@@ -9816,7 +9862,7 @@
         <v>1</v>
       </c>
       <c r="K219" t="s">
-        <v>728</v>
+        <v>710</v>
       </c>
       <c r="L219">
         <v>1</v>
@@ -10085,7 +10131,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" s="3" t="s">
         <v>434</v>
       </c>
@@ -10112,7 +10158,7 @@
         <v>31</v>
       </c>
       <c r="J230" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="K230" s="3" t="s">
         <v>405</v>
@@ -10126,7 +10172,7 @@
       <c r="N230" s="3"/>
       <c r="O230" s="3"/>
     </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" s="3" t="s">
         <v>434</v>
       </c>
@@ -10153,7 +10199,7 @@
         <v>17</v>
       </c>
       <c r="J231" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="K231" s="3"/>
       <c r="L231" s="3">
@@ -10217,7 +10263,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" s="3" t="s">
         <v>434</v>
       </c>
@@ -10244,7 +10290,7 @@
         <v>17</v>
       </c>
       <c r="J234" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="K234" s="3"/>
       <c r="L234" s="3">
@@ -10308,7 +10354,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" s="3" t="s">
         <v>434</v>
       </c>
@@ -10335,7 +10381,7 @@
         <v>17</v>
       </c>
       <c r="J237" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="K237" s="3" t="s">
         <v>456</v>
@@ -10349,7 +10395,7 @@
       <c r="N237" s="3"/>
       <c r="O237" s="3"/>
     </row>
-    <row r="238" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" s="3" t="s">
         <v>434</v>
       </c>
@@ -10376,7 +10422,7 @@
         <v>17</v>
       </c>
       <c r="J238" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="K238" s="3" t="s">
         <v>456</v>
@@ -10416,7 +10462,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="240" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" s="3" t="s">
         <v>434</v>
       </c>
@@ -10443,7 +10489,7 @@
         <v>17</v>
       </c>
       <c r="J240" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="K240" s="3"/>
       <c r="L240" s="3">
@@ -10559,7 +10605,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" s="3" t="s">
         <v>434</v>
       </c>
@@ -10588,7 +10634,7 @@
         <v>473</v>
       </c>
       <c r="J245" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="K245" s="3"/>
       <c r="L245" s="3">
@@ -10600,7 +10646,7 @@
       <c r="N245" s="3"/>
       <c r="O245" s="3"/>
     </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" s="3" t="s">
         <v>434</v>
       </c>
@@ -10629,7 +10675,7 @@
         <v>473</v>
       </c>
       <c r="J246" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="K246" s="3"/>
       <c r="L246" s="3">
@@ -10719,7 +10765,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" s="3" t="s">
         <v>434</v>
       </c>
@@ -10746,7 +10792,7 @@
         <v>17</v>
       </c>
       <c r="J250" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="K250" s="3"/>
       <c r="L250" s="3">
@@ -10758,7 +10804,7 @@
       <c r="N250" s="3"/>
       <c r="O250" s="3"/>
     </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" s="3" t="s">
         <v>434</v>
       </c>
@@ -10787,7 +10833,7 @@
         <v>473</v>
       </c>
       <c r="J251" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="K251" s="3"/>
       <c r="L251" s="3">
@@ -10799,7 +10845,7 @@
       <c r="N251" s="3"/>
       <c r="O251" s="3"/>
     </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>481</v>
       </c>
@@ -10941,7 +10987,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="257" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>481</v>
       </c>
@@ -10970,7 +11016,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="258" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>481</v>
       </c>
@@ -10999,45 +11045,48 @@
         <v>473</v>
       </c>
     </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A259" t="s">
+    <row r="259" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A259" s="6" t="s">
         <v>481</v>
       </c>
-      <c r="B259" t="s">
+      <c r="B259" s="6" t="s">
         <v>482</v>
       </c>
-      <c r="C259">
+      <c r="C259" s="6">
         <v>258</v>
       </c>
-      <c r="D259" t="s">
+      <c r="D259" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F259">
-        <v>0</v>
-      </c>
-      <c r="G259" t="s">
+      <c r="E259" s="6"/>
+      <c r="F259" s="6">
+        <v>0</v>
+      </c>
+      <c r="G259" s="6" t="s">
         <v>496</v>
       </c>
-      <c r="H259" t="s">
+      <c r="H259" s="6" t="s">
         <v>497</v>
       </c>
-      <c r="I259" t="s">
+      <c r="I259" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="J259" t="s">
-        <v>696</v>
-      </c>
-      <c r="K259" t="s">
-        <v>697</v>
-      </c>
-      <c r="L259">
+      <c r="J259" s="6" t="s">
+        <v>695</v>
+      </c>
+      <c r="K259" s="6" t="s">
+        <v>716</v>
+      </c>
+      <c r="L259" s="6">
         <v>2</v>
       </c>
-      <c r="M259" t="s">
+      <c r="M259" s="6" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="260" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+      <c r="N259" s="6"/>
+      <c r="O259" s="6"/>
+    </row>
+    <row r="260" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>481</v>
       </c>
@@ -11063,7 +11112,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="261" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>481</v>
       </c>
@@ -11089,7 +11138,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="262" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>481</v>
       </c>
@@ -11115,7 +11164,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="263" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>481</v>
       </c>
@@ -11141,7 +11190,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="264" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>481</v>
       </c>
@@ -11167,7 +11216,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="265" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>481</v>
       </c>
@@ -11193,7 +11242,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="266" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>481</v>
       </c>
@@ -11219,7 +11268,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="267" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>481</v>
       </c>
@@ -11245,7 +11294,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="268" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>481</v>
       </c>
@@ -11271,7 +11320,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="269" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>481</v>
       </c>
@@ -11297,7 +11346,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="270" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>481</v>
       </c>
@@ -11323,7 +11372,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="271" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>481</v>
       </c>
@@ -11349,7 +11398,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="272" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>481</v>
       </c>
@@ -11554,10 +11603,10 @@
         <v>31</v>
       </c>
       <c r="J279" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="K279" t="s">
-        <v>697</v>
+        <v>717</v>
       </c>
       <c r="L279">
         <v>2</v>
@@ -11592,10 +11641,10 @@
         <v>31</v>
       </c>
       <c r="J280" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="K280" t="s">
-        <v>540</v>
+        <v>718</v>
       </c>
       <c r="L280">
         <v>1</v>
@@ -11624,7 +11673,7 @@
         <v>538</v>
       </c>
       <c r="H281" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="I281" t="s">
         <v>74</v>
@@ -11647,10 +11696,10 @@
         <v>0</v>
       </c>
       <c r="G282" t="s">
+        <v>541</v>
+      </c>
+      <c r="H282" t="s">
         <v>542</v>
-      </c>
-      <c r="H282" t="s">
-        <v>543</v>
       </c>
       <c r="I282" t="s">
         <v>74</v>
@@ -11673,19 +11722,19 @@
         <v>0</v>
       </c>
       <c r="G283" t="s">
+        <v>543</v>
+      </c>
+      <c r="H283" t="s">
         <v>544</v>
-      </c>
-      <c r="H283" t="s">
-        <v>545</v>
       </c>
       <c r="I283" t="s">
         <v>31</v>
       </c>
       <c r="J283" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="K283" t="s">
-        <v>540</v>
+        <v>719</v>
       </c>
       <c r="L283">
         <v>1</v>
@@ -11711,10 +11760,10 @@
         <v>0</v>
       </c>
       <c r="G284" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H284" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="I284" t="s">
         <v>74</v>
@@ -11737,10 +11786,10 @@
         <v>1</v>
       </c>
       <c r="G285" t="s">
+        <v>546</v>
+      </c>
+      <c r="H285" t="s">
         <v>547</v>
-      </c>
-      <c r="H285" t="s">
-        <v>548</v>
       </c>
       <c r="I285" t="s">
         <v>17</v>
@@ -11763,10 +11812,10 @@
         <v>0</v>
       </c>
       <c r="G286" t="s">
+        <v>548</v>
+      </c>
+      <c r="H286" t="s">
         <v>549</v>
-      </c>
-      <c r="H286" t="s">
-        <v>550</v>
       </c>
       <c r="I286" t="s">
         <v>74</v>
@@ -11789,25 +11838,25 @@
         <v>0</v>
       </c>
       <c r="G287" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H287" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="I287" t="s">
         <v>31</v>
       </c>
       <c r="J287" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="K287" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="L287">
         <v>1</v>
       </c>
       <c r="M287" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="288" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
@@ -11827,16 +11876,16 @@
         <v>0</v>
       </c>
       <c r="G288" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H288" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="I288" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="289" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>481</v>
       </c>
@@ -11853,66 +11902,70 @@
         <v>0</v>
       </c>
       <c r="G289" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H289" t="s">
+        <v>553</v>
+      </c>
+      <c r="I289" t="s">
+        <v>17</v>
+      </c>
+      <c r="J289" t="s">
+        <v>695</v>
+      </c>
+      <c r="K289" t="s">
+        <v>721</v>
+      </c>
+      <c r="L289">
+        <v>1</v>
+      </c>
+      <c r="M289" t="s">
         <v>554</v>
       </c>
-      <c r="I289" t="s">
-        <v>17</v>
-      </c>
-      <c r="J289" t="s">
-        <v>696</v>
-      </c>
-      <c r="K289" t="s">
-        <v>725</v>
-      </c>
-      <c r="L289">
-        <v>1</v>
-      </c>
-      <c r="M289" t="s">
+    </row>
+    <row r="290" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A290" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="B290" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="C290" s="5">
+        <v>289</v>
+      </c>
+      <c r="D290" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E290" s="5"/>
+      <c r="F290" s="5">
+        <v>0</v>
+      </c>
+      <c r="G290" s="5" t="s">
         <v>555</v>
       </c>
-    </row>
-    <row r="290" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A290" t="s">
-        <v>481</v>
-      </c>
-      <c r="B290" t="s">
-        <v>498</v>
-      </c>
-      <c r="C290">
-        <v>289</v>
-      </c>
-      <c r="D290" t="s">
-        <v>28</v>
-      </c>
-      <c r="F290">
-        <v>0</v>
-      </c>
-      <c r="G290" t="s">
+      <c r="H290" s="5" t="s">
         <v>556</v>
       </c>
-      <c r="H290" t="s">
-        <v>557</v>
-      </c>
-      <c r="I290" t="s">
+      <c r="I290" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="J290" t="s">
-        <v>696</v>
-      </c>
-      <c r="K290" t="s">
-        <v>714</v>
-      </c>
-      <c r="L290">
-        <v>1</v>
-      </c>
-      <c r="M290" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="291" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="J290" s="5" t="s">
+        <v>695</v>
+      </c>
+      <c r="K290" s="5" t="s">
+        <v>722</v>
+      </c>
+      <c r="L290" s="5">
+        <v>1</v>
+      </c>
+      <c r="M290" s="5" t="s">
+        <v>551</v>
+      </c>
+      <c r="N290" s="5"/>
+      <c r="O290" s="5"/>
+      <c r="P290" s="5"/>
+    </row>
+    <row r="291" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>481</v>
       </c>
@@ -11929,69 +11982,71 @@
         <v>0</v>
       </c>
       <c r="G291" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H291" t="s">
+        <v>557</v>
+      </c>
+      <c r="I291" t="s">
+        <v>17</v>
+      </c>
+      <c r="J291" t="s">
+        <v>695</v>
+      </c>
+      <c r="K291" t="s">
+        <v>723</v>
+      </c>
+      <c r="L291">
+        <v>1</v>
+      </c>
+      <c r="M291" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="292" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A292" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="B292" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="C292" s="3">
+        <v>291</v>
+      </c>
+      <c r="D292" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E292" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F292" s="3">
+        <v>0</v>
+      </c>
+      <c r="G292" s="3" t="s">
         <v>558</v>
       </c>
-      <c r="I291" t="s">
-        <v>17</v>
-      </c>
-      <c r="J291" t="s">
-        <v>696</v>
-      </c>
-      <c r="K291" t="s">
-        <v>715</v>
-      </c>
-      <c r="L291">
-        <v>1</v>
-      </c>
-      <c r="M291" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A292" t="s">
-        <v>481</v>
-      </c>
-      <c r="B292" t="s">
-        <v>498</v>
-      </c>
-      <c r="C292">
-        <v>291</v>
-      </c>
-      <c r="D292" t="s">
-        <v>14</v>
-      </c>
-      <c r="E292" t="b">
-        <v>1</v>
-      </c>
-      <c r="F292">
-        <v>0</v>
-      </c>
-      <c r="G292" t="s">
+      <c r="H292" s="3" t="s">
         <v>559</v>
       </c>
-      <c r="H292" t="s">
+      <c r="I292" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="I292" t="s">
-        <v>561</v>
-      </c>
-      <c r="J292" t="s">
-        <v>696</v>
-      </c>
-      <c r="K292" t="s">
-        <v>721</v>
-      </c>
-      <c r="L292">
-        <v>1</v>
-      </c>
-      <c r="M292" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="293" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+      <c r="J292" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="K292" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="L292" s="3">
+        <v>1</v>
+      </c>
+      <c r="M292" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="N292" s="3"/>
+      <c r="O292" s="3"/>
+    </row>
+    <row r="293" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>481</v>
       </c>
@@ -12008,16 +12063,16 @@
         <v>0</v>
       </c>
       <c r="G293" t="s">
+        <v>561</v>
+      </c>
+      <c r="H293" t="s">
         <v>562</v>
-      </c>
-      <c r="H293" t="s">
-        <v>563</v>
       </c>
       <c r="I293" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="294" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>481</v>
       </c>
@@ -12034,16 +12089,16 @@
         <v>0</v>
       </c>
       <c r="G294" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H294" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="I294" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="295" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>481</v>
       </c>
@@ -12060,28 +12115,28 @@
         <v>0</v>
       </c>
       <c r="G295" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H295" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="I295" t="s">
         <v>17</v>
       </c>
       <c r="J295" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="K295" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="L295">
         <v>1</v>
       </c>
       <c r="M295" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="296" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="296" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>481</v>
       </c>
@@ -12098,16 +12153,16 @@
         <v>0</v>
       </c>
       <c r="G296" t="s">
+        <v>565</v>
+      </c>
+      <c r="H296" t="s">
         <v>566</v>
-      </c>
-      <c r="H296" t="s">
-        <v>567</v>
       </c>
       <c r="I296" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="297" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>481</v>
       </c>
@@ -12124,16 +12179,16 @@
         <v>0</v>
       </c>
       <c r="G297" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H297" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="I297" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="298" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>481</v>
       </c>
@@ -12150,28 +12205,28 @@
         <v>0</v>
       </c>
       <c r="G298" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H298" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I298" t="s">
         <v>17</v>
       </c>
       <c r="J298" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="K298" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="L298">
         <v>1</v>
       </c>
       <c r="M298" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.35">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="299" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>481</v>
       </c>
@@ -12188,28 +12243,28 @@
         <v>0</v>
       </c>
       <c r="G299" t="s">
+        <v>569</v>
+      </c>
+      <c r="H299" t="s">
         <v>570</v>
       </c>
-      <c r="H299" t="s">
+      <c r="I299" t="s">
+        <v>17</v>
+      </c>
+      <c r="J299" t="s">
+        <v>695</v>
+      </c>
+      <c r="K299" t="s">
+        <v>728</v>
+      </c>
+      <c r="L299">
+        <v>1</v>
+      </c>
+      <c r="M299" t="s">
         <v>571</v>
       </c>
-      <c r="I299" t="s">
-        <v>17</v>
-      </c>
-      <c r="J299" s="5" t="s">
-        <v>696</v>
-      </c>
-      <c r="K299" t="s">
-        <v>716</v>
-      </c>
-      <c r="L299">
-        <v>1</v>
-      </c>
-      <c r="M299" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="300" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="300" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>481</v>
       </c>
@@ -12226,28 +12281,28 @@
         <v>0</v>
       </c>
       <c r="G300" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H300" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I300" t="s">
         <v>31</v>
       </c>
-      <c r="J300" s="5" t="s">
-        <v>696</v>
+      <c r="J300" t="s">
+        <v>695</v>
       </c>
       <c r="K300" t="s">
-        <v>717</v>
+        <v>729</v>
       </c>
       <c r="L300">
         <v>1</v>
       </c>
       <c r="M300" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="301" spans="1:13" x14ac:dyDescent="0.35">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="301" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>481</v>
       </c>
@@ -12264,25 +12319,28 @@
         <v>0</v>
       </c>
       <c r="G301" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H301" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="I301" t="s">
         <v>17</v>
       </c>
-      <c r="J301" s="5" t="s">
-        <v>696</v>
+      <c r="J301" t="s">
+        <v>695</v>
+      </c>
+      <c r="K301" t="s">
+        <v>727</v>
       </c>
       <c r="L301">
         <v>1</v>
       </c>
       <c r="M301" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="302" spans="1:13" x14ac:dyDescent="0.35">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="302" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>481</v>
       </c>
@@ -12299,28 +12357,28 @@
         <v>0</v>
       </c>
       <c r="G302" t="s">
+        <v>574</v>
+      </c>
+      <c r="H302" t="s">
         <v>575</v>
       </c>
-      <c r="H302" t="s">
-        <v>576</v>
-      </c>
       <c r="I302" t="s">
         <v>17</v>
       </c>
-      <c r="J302" s="5" t="s">
-        <v>696</v>
+      <c r="J302" t="s">
+        <v>695</v>
       </c>
       <c r="K302" t="s">
-        <v>720</v>
+        <v>731</v>
       </c>
       <c r="L302">
         <v>1</v>
       </c>
       <c r="M302" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.35">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="303" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>481</v>
       </c>
@@ -12337,28 +12395,28 @@
         <v>0</v>
       </c>
       <c r="G303" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H303" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="I303" t="s">
         <v>17</v>
       </c>
-      <c r="J303" s="5" t="s">
-        <v>696</v>
+      <c r="J303" t="s">
+        <v>695</v>
       </c>
       <c r="K303" t="s">
-        <v>720</v>
+        <v>730</v>
       </c>
       <c r="L303">
         <v>1</v>
       </c>
       <c r="M303" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="304" spans="1:13" x14ac:dyDescent="0.35">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="304" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>481</v>
       </c>
@@ -12375,28 +12433,28 @@
         <v>0</v>
       </c>
       <c r="G304" t="s">
+        <v>576</v>
+      </c>
+      <c r="H304" t="s">
         <v>577</v>
       </c>
-      <c r="H304" t="s">
-        <v>578</v>
-      </c>
       <c r="I304" t="s">
         <v>17</v>
       </c>
-      <c r="J304" s="5" t="s">
-        <v>696</v>
+      <c r="J304" t="s">
+        <v>695</v>
       </c>
       <c r="K304" t="s">
-        <v>720</v>
+        <v>731</v>
       </c>
       <c r="L304">
         <v>1</v>
       </c>
       <c r="M304" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="305" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="305" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>481</v>
       </c>
@@ -12413,16 +12471,16 @@
         <v>0</v>
       </c>
       <c r="G305" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H305" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="I305" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="306" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>481</v>
       </c>
@@ -12442,48 +12500,51 @@
         <v>0</v>
       </c>
       <c r="G306" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="307" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A307" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="B307" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="C307" s="3">
+        <v>306</v>
+      </c>
+      <c r="D307" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E307" s="3"/>
+      <c r="F307" s="3">
+        <v>0</v>
+      </c>
+      <c r="G307" s="3" t="s">
         <v>579</v>
       </c>
-    </row>
-    <row r="307" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A307" t="s">
-        <v>481</v>
-      </c>
-      <c r="B307" t="s">
-        <v>498</v>
-      </c>
-      <c r="C307">
-        <v>306</v>
-      </c>
-      <c r="D307" t="s">
-        <v>14</v>
-      </c>
-      <c r="F307">
-        <v>0</v>
-      </c>
-      <c r="G307" t="s">
+      <c r="H307" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="H307" t="s">
-        <v>581</v>
-      </c>
-      <c r="I307" t="s">
-        <v>17</v>
-      </c>
-      <c r="J307" s="5" t="s">
-        <v>696</v>
-      </c>
-      <c r="K307" t="s">
-        <v>718</v>
-      </c>
-      <c r="L307">
-        <v>1</v>
-      </c>
-      <c r="M307" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="308" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="I307" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J307" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="K307" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="L307" s="3">
+        <v>1</v>
+      </c>
+      <c r="M307" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="N307" s="3"/>
+      <c r="O307" s="3"/>
+    </row>
+    <row r="308" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>481</v>
       </c>
@@ -12500,28 +12561,28 @@
         <v>0</v>
       </c>
       <c r="G308" t="s">
+        <v>581</v>
+      </c>
+      <c r="H308" t="s">
         <v>582</v>
       </c>
-      <c r="H308" t="s">
+      <c r="I308" t="s">
+        <v>17</v>
+      </c>
+      <c r="J308" t="s">
+        <v>696</v>
+      </c>
+      <c r="K308" t="s">
+        <v>711</v>
+      </c>
+      <c r="L308">
+        <v>1</v>
+      </c>
+      <c r="M308" t="s">
         <v>583</v>
       </c>
-      <c r="I308" t="s">
-        <v>17</v>
-      </c>
-      <c r="J308" s="5" t="s">
-        <v>719</v>
-      </c>
-      <c r="K308" t="s">
-        <v>729</v>
-      </c>
-      <c r="L308">
-        <v>1</v>
-      </c>
-      <c r="M308" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="309" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="309" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>481</v>
       </c>
@@ -12541,21 +12602,21 @@
         <v>0</v>
       </c>
       <c r="G309" t="s">
+        <v>584</v>
+      </c>
+      <c r="H309" t="s">
         <v>585</v>
       </c>
-      <c r="H309" t="s">
+      <c r="I309" t="s">
         <v>586</v>
       </c>
-      <c r="I309" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="310" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="310" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>481</v>
       </c>
       <c r="B310" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C310">
         <v>309</v>
@@ -12570,15 +12631,15 @@
         <v>1</v>
       </c>
       <c r="G310" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="311" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="311" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>481</v>
       </c>
       <c r="B311" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C311">
         <v>310</v>
@@ -12593,15 +12654,15 @@
         <v>1</v>
       </c>
       <c r="G311" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="312" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="312" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>481</v>
       </c>
       <c r="B312" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C312">
         <v>311</v>
@@ -12613,21 +12674,21 @@
         <v>1</v>
       </c>
       <c r="G312" t="s">
+        <v>590</v>
+      </c>
+      <c r="H312" t="s">
         <v>591</v>
       </c>
-      <c r="H312" t="s">
-        <v>592</v>
-      </c>
       <c r="I312" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="313" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>481</v>
       </c>
       <c r="B313" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C313">
         <v>312</v>
@@ -12639,21 +12700,21 @@
         <v>1</v>
       </c>
       <c r="G313" t="s">
+        <v>593</v>
+      </c>
+      <c r="H313" t="s">
         <v>594</v>
       </c>
-      <c r="H313" t="s">
-        <v>595</v>
-      </c>
       <c r="I313" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="314" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>481</v>
       </c>
       <c r="B314" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C314">
         <v>313</v>
@@ -12665,21 +12726,21 @@
         <v>1</v>
       </c>
       <c r="G314" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H314" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="I314" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="315" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>481</v>
       </c>
       <c r="B315" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C315">
         <v>314</v>
@@ -12691,21 +12752,21 @@
         <v>1</v>
       </c>
       <c r="G315" t="s">
+        <v>597</v>
+      </c>
+      <c r="H315" t="s">
         <v>598</v>
       </c>
-      <c r="H315" t="s">
-        <v>599</v>
-      </c>
       <c r="I315" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>481</v>
       </c>
       <c r="B316" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C316">
         <v>315</v>
@@ -12717,33 +12778,33 @@
         <v>0</v>
       </c>
       <c r="G316" t="s">
+        <v>599</v>
+      </c>
+      <c r="H316" t="s">
         <v>600</v>
       </c>
-      <c r="H316" t="s">
+      <c r="I316" t="s">
+        <v>17</v>
+      </c>
+      <c r="J316" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="K316" t="s">
         <v>601</v>
-      </c>
-      <c r="I316" t="s">
-        <v>17</v>
-      </c>
-      <c r="J316" s="4" t="s">
-        <v>698</v>
-      </c>
-      <c r="K316" t="s">
-        <v>602</v>
       </c>
       <c r="L316">
         <v>2</v>
       </c>
       <c r="M316" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="317" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="317" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>481</v>
       </c>
       <c r="B317" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C317">
         <v>316</v>
@@ -12755,21 +12816,21 @@
         <v>1</v>
       </c>
       <c r="G317" t="s">
+        <v>603</v>
+      </c>
+      <c r="H317" t="s">
         <v>604</v>
       </c>
-      <c r="H317" t="s">
-        <v>605</v>
-      </c>
       <c r="I317" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="318" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>481</v>
       </c>
       <c r="B318" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C318">
         <v>317</v>
@@ -12781,21 +12842,21 @@
         <v>1</v>
       </c>
       <c r="G318" t="s">
+        <v>605</v>
+      </c>
+      <c r="H318" t="s">
         <v>606</v>
       </c>
-      <c r="H318" t="s">
-        <v>607</v>
-      </c>
       <c r="I318" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="319" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>481</v>
       </c>
       <c r="B319" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C319">
         <v>318</v>
@@ -12807,21 +12868,21 @@
         <v>1</v>
       </c>
       <c r="G319" t="s">
+        <v>607</v>
+      </c>
+      <c r="H319" t="s">
         <v>608</v>
-      </c>
-      <c r="H319" t="s">
-        <v>609</v>
       </c>
       <c r="I319" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="320" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>481</v>
       </c>
       <c r="B320" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C320">
         <v>319</v>
@@ -12833,21 +12894,21 @@
         <v>1</v>
       </c>
       <c r="G320" t="s">
+        <v>609</v>
+      </c>
+      <c r="H320" t="s">
         <v>610</v>
       </c>
-      <c r="H320" t="s">
-        <v>611</v>
-      </c>
       <c r="I320" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="321" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>481</v>
       </c>
       <c r="B321" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C321">
         <v>320</v>
@@ -12859,33 +12920,33 @@
         <v>0</v>
       </c>
       <c r="G321" t="s">
+        <v>611</v>
+      </c>
+      <c r="H321" t="s">
         <v>612</v>
       </c>
-      <c r="H321" t="s">
-        <v>613</v>
-      </c>
       <c r="I321" t="s">
         <v>17</v>
       </c>
       <c r="J321" s="4" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K321" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="L321">
         <v>2</v>
       </c>
       <c r="M321" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="322" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="322" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>481</v>
       </c>
       <c r="B322" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C322">
         <v>321</v>
@@ -12897,21 +12958,21 @@
         <v>1</v>
       </c>
       <c r="G322" t="s">
+        <v>614</v>
+      </c>
+      <c r="H322" t="s">
         <v>615</v>
       </c>
-      <c r="H322" t="s">
-        <v>616</v>
-      </c>
       <c r="I322" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="323" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>481</v>
       </c>
       <c r="B323" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C323">
         <v>322</v>
@@ -12923,33 +12984,33 @@
         <v>0</v>
       </c>
       <c r="G323" t="s">
+        <v>616</v>
+      </c>
+      <c r="H323" t="s">
         <v>617</v>
       </c>
-      <c r="H323" t="s">
-        <v>618</v>
-      </c>
       <c r="I323" t="s">
         <v>17</v>
       </c>
       <c r="J323" s="4" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K323" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="L323">
         <v>2</v>
       </c>
       <c r="M323" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="324" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="324" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>481</v>
       </c>
       <c r="B324" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C324">
         <v>323</v>
@@ -12961,21 +13022,21 @@
         <v>1</v>
       </c>
       <c r="G324" t="s">
+        <v>619</v>
+      </c>
+      <c r="H324" t="s">
         <v>620</v>
       </c>
-      <c r="H324" t="s">
-        <v>621</v>
-      </c>
       <c r="I324" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="325" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>481</v>
       </c>
       <c r="B325" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C325">
         <v>324</v>
@@ -12987,16 +13048,16 @@
         <v>0</v>
       </c>
       <c r="G325" t="s">
+        <v>621</v>
+      </c>
+      <c r="H325" t="s">
         <v>622</v>
       </c>
-      <c r="H325" t="s">
-        <v>623</v>
-      </c>
       <c r="I325" t="s">
         <v>17</v>
       </c>
       <c r="J325" s="4" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K325" t="s">
         <v>405</v>
@@ -13005,15 +13066,15 @@
         <v>2</v>
       </c>
       <c r="M325" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="326" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="326" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>481</v>
       </c>
       <c r="B326" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C326">
         <v>325</v>
@@ -13025,59 +13086,62 @@
         <v>1</v>
       </c>
       <c r="G326" t="s">
+        <v>624</v>
+      </c>
+      <c r="H326" t="s">
         <v>625</v>
       </c>
-      <c r="H326" t="s">
+      <c r="I326" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="327" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A327" s="5" t="s">
         <v>626</v>
       </c>
-      <c r="I326" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="327" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A327" t="s">
+      <c r="B327" s="5" t="s">
         <v>627</v>
       </c>
-      <c r="B327" t="s">
+      <c r="C327" s="5">
+        <v>326</v>
+      </c>
+      <c r="D327" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E327" s="5"/>
+      <c r="F327" s="5">
+        <v>0</v>
+      </c>
+      <c r="G327" s="5" t="s">
         <v>628</v>
       </c>
-      <c r="C327">
-        <v>326</v>
-      </c>
-      <c r="D327" t="s">
-        <v>14</v>
-      </c>
-      <c r="F327">
-        <v>0</v>
-      </c>
-      <c r="G327" t="s">
+      <c r="H327" s="5" t="s">
         <v>629</v>
       </c>
-      <c r="H327" t="s">
-        <v>630</v>
-      </c>
-      <c r="I327" t="s">
+      <c r="I327" s="5" t="s">
         <v>17</v>
       </c>
       <c r="J327" s="5" t="s">
-        <v>696</v>
-      </c>
-      <c r="K327" t="s">
-        <v>726</v>
-      </c>
-      <c r="L327">
+        <v>695</v>
+      </c>
+      <c r="K327" s="5" t="s">
+        <v>733</v>
+      </c>
+      <c r="L327" s="5">
         <v>2</v>
       </c>
-      <c r="M327" t="s">
+      <c r="M327" s="5" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="328" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+      <c r="N327" s="5"/>
+      <c r="O327" s="5"/>
+    </row>
+    <row r="328" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
+        <v>626</v>
+      </c>
+      <c r="B328" t="s">
         <v>627</v>
-      </c>
-      <c r="B328" t="s">
-        <v>628</v>
       </c>
       <c r="C328">
         <v>327</v>
@@ -13089,21 +13153,21 @@
         <v>0</v>
       </c>
       <c r="G328" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H328" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="I328" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="329" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
+        <v>626</v>
+      </c>
+      <c r="B329" t="s">
         <v>627</v>
-      </c>
-      <c r="B329" t="s">
-        <v>628</v>
       </c>
       <c r="C329">
         <v>328</v>
@@ -13115,16 +13179,19 @@
         <v>0</v>
       </c>
       <c r="G329" t="s">
+        <v>631</v>
+      </c>
+      <c r="H329" t="s">
         <v>632</v>
       </c>
-      <c r="H329" t="s">
-        <v>633</v>
-      </c>
       <c r="I329" t="s">
         <v>17</v>
       </c>
-      <c r="J329" s="5" t="s">
-        <v>696</v>
+      <c r="J329" t="s">
+        <v>695</v>
+      </c>
+      <c r="K329" t="s">
+        <v>734</v>
       </c>
       <c r="L329">
         <v>1</v>
@@ -13133,12 +13200,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="330" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
+        <v>626</v>
+      </c>
+      <c r="B330" t="s">
         <v>627</v>
-      </c>
-      <c r="B330" t="s">
-        <v>628</v>
       </c>
       <c r="C330">
         <v>329</v>
@@ -13150,211 +13217,226 @@
         <v>0</v>
       </c>
       <c r="G330" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H330" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="I330" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="331" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A331" t="s">
+    <row r="331" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A331" s="6" t="s">
+        <v>626</v>
+      </c>
+      <c r="B331" s="6" t="s">
         <v>627</v>
       </c>
-      <c r="B331" t="s">
-        <v>628</v>
-      </c>
-      <c r="C331">
+      <c r="C331" s="6">
         <v>330</v>
       </c>
-      <c r="D331" t="s">
-        <v>14</v>
-      </c>
-      <c r="F331">
-        <v>0</v>
-      </c>
-      <c r="G331" t="s">
+      <c r="D331" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E331" s="6"/>
+      <c r="F331" s="6">
+        <v>0</v>
+      </c>
+      <c r="G331" s="6" t="s">
+        <v>634</v>
+      </c>
+      <c r="H331" s="6" t="s">
         <v>635</v>
       </c>
-      <c r="H331" t="s">
+      <c r="I331" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J331" s="6" t="s">
+        <v>695</v>
+      </c>
+      <c r="K331" s="6" t="s">
+        <v>735</v>
+      </c>
+      <c r="L331" s="6">
+        <v>2</v>
+      </c>
+      <c r="M331" s="6" t="s">
+        <v>554</v>
+      </c>
+      <c r="N331" s="6"/>
+      <c r="O331" s="6"/>
+    </row>
+    <row r="332" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A332" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="B332" s="3" t="s">
         <v>636</v>
       </c>
-      <c r="I331" t="s">
-        <v>17</v>
-      </c>
-      <c r="J331" s="5" t="s">
-        <v>696</v>
-      </c>
-      <c r="K331" t="s">
-        <v>485</v>
-      </c>
-      <c r="L331">
+      <c r="C332" s="3">
+        <v>331</v>
+      </c>
+      <c r="D332" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E332" s="3"/>
+      <c r="F332" s="3">
+        <v>0</v>
+      </c>
+      <c r="G332" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="H332" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="I332" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J332" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="K332" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="L332" s="3">
+        <v>1</v>
+      </c>
+      <c r="M332" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="N332" s="3"/>
+      <c r="O332" s="3"/>
+    </row>
+    <row r="333" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A333" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="B333" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="C333" s="3">
+        <v>332</v>
+      </c>
+      <c r="D333" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E333" s="3"/>
+      <c r="F333" s="3">
+        <v>0</v>
+      </c>
+      <c r="G333" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="H333" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="I333" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J333" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="K333" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="L333" s="3">
+        <v>1</v>
+      </c>
+      <c r="M333" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="N333" s="3"/>
+      <c r="O333" s="3"/>
+    </row>
+    <row r="334" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A334" s="6" t="s">
+        <v>626</v>
+      </c>
+      <c r="B334" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="C334" s="6">
+        <v>333</v>
+      </c>
+      <c r="D334" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E334" s="6"/>
+      <c r="F334" s="6">
+        <v>0</v>
+      </c>
+      <c r="G334" s="6" t="s">
+        <v>641</v>
+      </c>
+      <c r="H334" s="6" t="s">
+        <v>642</v>
+      </c>
+      <c r="I334" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J334" s="6" t="s">
+        <v>695</v>
+      </c>
+      <c r="K334" s="6" t="s">
+        <v>698</v>
+      </c>
+      <c r="L334" s="6">
         <v>2</v>
       </c>
-      <c r="M331" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="332" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A332" t="s">
-        <v>627</v>
-      </c>
-      <c r="B332" t="s">
-        <v>637</v>
-      </c>
-      <c r="C332">
-        <v>331</v>
-      </c>
-      <c r="D332" t="s">
-        <v>14</v>
-      </c>
-      <c r="F332">
-        <v>0</v>
-      </c>
-      <c r="G332" t="s">
-        <v>638</v>
-      </c>
-      <c r="H332" t="s">
+      <c r="M334" s="6" t="s">
         <v>639</v>
       </c>
-      <c r="I332" t="s">
-        <v>17</v>
-      </c>
-      <c r="J332" t="s">
-        <v>696</v>
-      </c>
-      <c r="K332" t="s">
-        <v>699</v>
-      </c>
-      <c r="L332">
-        <v>1</v>
-      </c>
-      <c r="M332" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="333" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A333" t="s">
-        <v>627</v>
-      </c>
-      <c r="B333" t="s">
-        <v>637</v>
-      </c>
-      <c r="C333">
-        <v>332</v>
-      </c>
-      <c r="D333" t="s">
-        <v>14</v>
-      </c>
-      <c r="F333">
-        <v>0</v>
-      </c>
-      <c r="G333" t="s">
-        <v>638</v>
-      </c>
-      <c r="H333" t="s">
-        <v>641</v>
-      </c>
-      <c r="I333" t="s">
-        <v>17</v>
-      </c>
-      <c r="J333" t="s">
-        <v>696</v>
-      </c>
-      <c r="K333" t="s">
-        <v>699</v>
-      </c>
-      <c r="L333">
-        <v>1</v>
-      </c>
-      <c r="M333" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="334" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A334" t="s">
-        <v>627</v>
-      </c>
-      <c r="B334" t="s">
-        <v>637</v>
-      </c>
-      <c r="C334">
-        <v>333</v>
-      </c>
-      <c r="D334" t="s">
-        <v>14</v>
-      </c>
-      <c r="F334">
-        <v>0</v>
-      </c>
-      <c r="G334" t="s">
-        <v>642</v>
-      </c>
-      <c r="H334" t="s">
+      <c r="N334" s="6"/>
+      <c r="O334" s="6"/>
+    </row>
+    <row r="335" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A335" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="I334" t="s">
-        <v>17</v>
-      </c>
-      <c r="J334" t="s">
-        <v>696</v>
-      </c>
-      <c r="K334" t="s">
-        <v>700</v>
-      </c>
-      <c r="L334">
+      <c r="B335" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="C335" s="3">
+        <v>334</v>
+      </c>
+      <c r="D335" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E335" s="3"/>
+      <c r="F335" s="3">
+        <v>0</v>
+      </c>
+      <c r="G335" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="H335" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="I335" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J335" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="K335" s="3" t="s">
+        <v>736</v>
+      </c>
+      <c r="L335" s="3">
         <v>2</v>
       </c>
-      <c r="M334" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="335" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A335" t="s">
+      <c r="M335" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N335" s="3"/>
+      <c r="O335" s="3"/>
+    </row>
+    <row r="336" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A336" t="s">
+        <v>643</v>
+      </c>
+      <c r="B336" t="s">
         <v>644</v>
-      </c>
-      <c r="B335" t="s">
-        <v>645</v>
-      </c>
-      <c r="C335">
-        <v>334</v>
-      </c>
-      <c r="D335" t="s">
-        <v>14</v>
-      </c>
-      <c r="F335">
-        <v>0</v>
-      </c>
-      <c r="G335" t="s">
-        <v>646</v>
-      </c>
-      <c r="H335" t="s">
-        <v>647</v>
-      </c>
-      <c r="I335" t="s">
-        <v>17</v>
-      </c>
-      <c r="J335" s="5" t="s">
-        <v>696</v>
-      </c>
-      <c r="K335" t="s">
-        <v>707</v>
-      </c>
-      <c r="L335">
-        <v>2</v>
-      </c>
-      <c r="M335" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="336" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A336" t="s">
-        <v>644</v>
-      </c>
-      <c r="B336" t="s">
-        <v>645</v>
       </c>
       <c r="C336">
         <v>335</v>
@@ -13366,59 +13448,62 @@
         <v>0</v>
       </c>
       <c r="G336" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H336" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="I336" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="337" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A337" t="s">
+    <row r="337" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A337" s="5" t="s">
+        <v>643</v>
+      </c>
+      <c r="B337" s="5" t="s">
         <v>644</v>
       </c>
-      <c r="B337" t="s">
-        <v>645</v>
-      </c>
-      <c r="C337">
+      <c r="C337" s="5">
         <v>336</v>
       </c>
-      <c r="D337" t="s">
-        <v>14</v>
-      </c>
-      <c r="F337">
-        <v>0</v>
-      </c>
-      <c r="G337" t="s">
-        <v>649</v>
-      </c>
-      <c r="H337" t="s">
-        <v>647</v>
-      </c>
-      <c r="I337" t="s">
+      <c r="D337" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E337" s="5"/>
+      <c r="F337" s="5">
+        <v>0</v>
+      </c>
+      <c r="G337" s="5" t="s">
+        <v>648</v>
+      </c>
+      <c r="H337" s="5" t="s">
+        <v>646</v>
+      </c>
+      <c r="I337" s="5" t="s">
         <v>17</v>
       </c>
       <c r="J337" s="5" t="s">
-        <v>696</v>
-      </c>
-      <c r="K337" t="s">
-        <v>708</v>
-      </c>
-      <c r="L337">
+        <v>695</v>
+      </c>
+      <c r="K337" s="5" t="s">
+        <v>737</v>
+      </c>
+      <c r="L337" s="5">
         <v>2</v>
       </c>
-      <c r="M337" t="s">
+      <c r="M337" s="5" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="338" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+      <c r="N337" s="5"/>
+      <c r="O337" s="5"/>
+    </row>
+    <row r="338" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
+        <v>643</v>
+      </c>
+      <c r="B338" t="s">
         <v>644</v>
-      </c>
-      <c r="B338" t="s">
-        <v>645</v>
       </c>
       <c r="C338">
         <v>337</v>
@@ -13430,97 +13515,103 @@
         <v>0</v>
       </c>
       <c r="G338" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H338" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="I338" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="339" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A339" t="s">
+    <row r="339" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A339" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="B339" s="7" t="s">
         <v>644</v>
       </c>
-      <c r="B339" t="s">
-        <v>645</v>
-      </c>
-      <c r="C339">
+      <c r="C339" s="7">
         <v>338</v>
       </c>
-      <c r="D339" t="s">
-        <v>14</v>
-      </c>
-      <c r="F339">
-        <v>0</v>
-      </c>
-      <c r="G339" t="s">
+      <c r="D339" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E339" s="7"/>
+      <c r="F339" s="7">
+        <v>0</v>
+      </c>
+      <c r="G339" s="7" t="s">
+        <v>650</v>
+      </c>
+      <c r="H339" s="7" t="s">
+        <v>646</v>
+      </c>
+      <c r="I339" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J339" s="7" t="s">
+        <v>695</v>
+      </c>
+      <c r="K339" s="7" t="s">
+        <v>706</v>
+      </c>
+      <c r="L339" s="7">
+        <v>1</v>
+      </c>
+      <c r="M339" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N339" s="7"/>
+      <c r="O339" s="7"/>
+    </row>
+    <row r="340" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A340" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="B340" s="7" t="s">
+        <v>644</v>
+      </c>
+      <c r="C340" s="7">
+        <v>339</v>
+      </c>
+      <c r="D340" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E340" s="7"/>
+      <c r="F340" s="7">
+        <v>0</v>
+      </c>
+      <c r="G340" s="7" t="s">
         <v>651</v>
       </c>
-      <c r="H339" t="s">
-        <v>647</v>
-      </c>
-      <c r="I339" t="s">
-        <v>17</v>
-      </c>
-      <c r="J339" s="5" t="s">
-        <v>696</v>
-      </c>
-      <c r="K339" t="s">
-        <v>710</v>
-      </c>
-      <c r="L339">
-        <v>1</v>
-      </c>
-      <c r="M339" t="s">
+      <c r="H340" s="7" t="s">
+        <v>646</v>
+      </c>
+      <c r="I340" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J340" s="7" t="s">
+        <v>695</v>
+      </c>
+      <c r="K340" s="7" t="s">
+        <v>705</v>
+      </c>
+      <c r="L340" s="7">
+        <v>1</v>
+      </c>
+      <c r="M340" s="7" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="340" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A340" t="s">
-        <v>644</v>
-      </c>
-      <c r="B340" t="s">
-        <v>645</v>
-      </c>
-      <c r="C340">
-        <v>339</v>
-      </c>
-      <c r="D340" t="s">
-        <v>28</v>
-      </c>
-      <c r="F340">
-        <v>0</v>
-      </c>
-      <c r="G340" t="s">
+      <c r="N340" s="7"/>
+      <c r="O340" s="7"/>
+    </row>
+    <row r="341" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A341" t="s">
+        <v>643</v>
+      </c>
+      <c r="B341" t="s">
         <v>652</v>
-      </c>
-      <c r="H340" t="s">
-        <v>647</v>
-      </c>
-      <c r="I340" t="s">
-        <v>31</v>
-      </c>
-      <c r="J340" s="5" t="s">
-        <v>696</v>
-      </c>
-      <c r="K340" t="s">
-        <v>709</v>
-      </c>
-      <c r="L340">
-        <v>1</v>
-      </c>
-      <c r="M340" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="341" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A341" t="s">
-        <v>644</v>
-      </c>
-      <c r="B341" t="s">
-        <v>653</v>
       </c>
       <c r="C341">
         <v>340</v>
@@ -13532,21 +13623,21 @@
         <v>1</v>
       </c>
       <c r="G341" t="s">
+        <v>653</v>
+      </c>
+      <c r="H341" t="s">
         <v>654</v>
-      </c>
-      <c r="H341" t="s">
-        <v>655</v>
       </c>
       <c r="I341" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="342" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B342" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C342">
         <v>341</v>
@@ -13558,59 +13649,62 @@
         <v>1</v>
       </c>
       <c r="G342" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H342" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="I342" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="343" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A343" t="s">
-        <v>644</v>
-      </c>
-      <c r="B343" t="s">
-        <v>653</v>
-      </c>
-      <c r="C343">
+    <row r="343" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A343" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="B343" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="C343" s="3">
         <v>342</v>
       </c>
-      <c r="D343" t="s">
-        <v>14</v>
-      </c>
-      <c r="F343">
-        <v>0</v>
-      </c>
-      <c r="G343" t="s">
-        <v>657</v>
-      </c>
-      <c r="H343" t="s">
+      <c r="D343" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E343" s="3"/>
+      <c r="F343" s="3">
+        <v>0</v>
+      </c>
+      <c r="G343" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="H343" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="I343" t="s">
-        <v>17</v>
-      </c>
-      <c r="J343" s="5" t="s">
-        <v>696</v>
-      </c>
-      <c r="K343" t="s">
-        <v>711</v>
-      </c>
-      <c r="L343">
+      <c r="I343" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J343" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="K343" s="3" t="s">
+        <v>736</v>
+      </c>
+      <c r="L343" s="3">
         <v>2</v>
       </c>
-      <c r="M343" t="s">
+      <c r="M343" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="344" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+      <c r="N343" s="3"/>
+      <c r="O343" s="3"/>
+    </row>
+    <row r="344" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B344" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C344">
         <v>343</v>
@@ -13622,21 +13716,21 @@
         <v>1</v>
       </c>
       <c r="G344" t="s">
+        <v>657</v>
+      </c>
+      <c r="H344" t="s">
         <v>658</v>
       </c>
-      <c r="H344" t="s">
-        <v>659</v>
-      </c>
       <c r="I344" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="345" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B345" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C345">
         <v>344</v>
@@ -13648,90 +13742,96 @@
         <v>1</v>
       </c>
       <c r="G345" t="s">
+        <v>659</v>
+      </c>
+      <c r="H345" t="s">
         <v>660</v>
       </c>
-      <c r="H345" t="s">
+      <c r="I345" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="346" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A346" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="B346" s="8" t="s">
+        <v>652</v>
+      </c>
+      <c r="C346" s="8">
+        <v>345</v>
+      </c>
+      <c r="D346" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E346" s="8"/>
+      <c r="F346" s="8">
+        <v>0</v>
+      </c>
+      <c r="G346" s="8" t="s">
         <v>661</v>
       </c>
-      <c r="I345" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="346" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A346" t="s">
-        <v>644</v>
-      </c>
-      <c r="B346" t="s">
-        <v>653</v>
-      </c>
-      <c r="C346">
-        <v>345</v>
-      </c>
-      <c r="D346" t="s">
-        <v>14</v>
-      </c>
-      <c r="F346">
-        <v>0</v>
-      </c>
-      <c r="G346" t="s">
+      <c r="H346" s="8" t="s">
+        <v>656</v>
+      </c>
+      <c r="I346" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J346" s="8" t="s">
+        <v>695</v>
+      </c>
+      <c r="K346" s="8" t="s">
+        <v>707</v>
+      </c>
+      <c r="L346" s="8">
+        <v>1</v>
+      </c>
+      <c r="M346" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="N346" s="8"/>
+      <c r="O346" s="8"/>
+    </row>
+    <row r="347" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A347" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="B347" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="C347" s="3">
+        <v>346</v>
+      </c>
+      <c r="D347" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E347" s="3"/>
+      <c r="F347" s="3">
+        <v>0</v>
+      </c>
+      <c r="G347" s="3" t="s">
         <v>662</v>
       </c>
-      <c r="H346" t="s">
-        <v>657</v>
-      </c>
-      <c r="I346" t="s">
-        <v>17</v>
-      </c>
-      <c r="J346" s="5" t="s">
-        <v>696</v>
-      </c>
-      <c r="K346" t="s">
-        <v>712</v>
-      </c>
-      <c r="L346">
-        <v>1</v>
-      </c>
-      <c r="M346" t="s">
+      <c r="H347" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="I347" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J347" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="K347" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="L347" s="3">
+        <v>1</v>
+      </c>
+      <c r="M347" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="347" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A347" t="s">
-        <v>644</v>
-      </c>
-      <c r="B347" t="s">
-        <v>653</v>
-      </c>
-      <c r="C347">
-        <v>346</v>
-      </c>
-      <c r="D347" t="s">
-        <v>14</v>
-      </c>
-      <c r="F347">
-        <v>0</v>
-      </c>
-      <c r="G347" t="s">
-        <v>663</v>
-      </c>
-      <c r="H347" t="s">
-        <v>664</v>
-      </c>
-      <c r="I347" t="s">
-        <v>17</v>
-      </c>
-      <c r="J347" s="5" t="s">
-        <v>696</v>
-      </c>
-      <c r="K347" t="s">
-        <v>713</v>
-      </c>
-      <c r="L347">
-        <v>1</v>
-      </c>
-      <c r="M347" t="s">
-        <v>27</v>
-      </c>
+      <c r="N347" s="3"/>
+      <c r="O347" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M347" xr:uid="{184E8DB1-1DA0-4161-AC11-ADA355556CCF}">
@@ -13746,6 +13846,11 @@
         <filter val="0"/>
       </filters>
     </filterColumn>
+    <filterColumn colId="9">
+      <filters>
+        <filter val="tad-1"/>
+      </filters>
+    </filterColumn>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/fracas/fracas_worksheet.xlsx
+++ b/fracas/fracas_worksheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ivorm\yarn2fol\fracas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37116522-A98F-4D1D-8187-72A533ED3E89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1632A57-8AE7-4A78-8204-899843F9DD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{DDDA1AFE-174D-47B1-8070-326023C11386}"/>
   </bookViews>
@@ -18,13 +18,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">fracas!$A$1:$M$347</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2374" uniqueCount="738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2369" uniqueCount="740">
   <si>
     <t>section</t>
   </si>
@@ -1829,9 +1841,6 @@
     <t>Smith had been travelling the day before she arrived in Katmandu.</t>
   </si>
   <si>
-    <t>complex temporal reasoning</t>
-  </si>
-  <si>
     <t>temp, quant, num, def, duration, BEFORE</t>
   </si>
   <si>
@@ -2045,9 +2054,6 @@
     <t>negation of singular</t>
   </si>
   <si>
-    <t>at least a few?</t>
-  </si>
-  <si>
     <t>mass noun; 'at home' ambiguous possession; modeled as non-core AMR role</t>
   </si>
   <si>
@@ -2238,13 +2244,25 @@
   </si>
   <si>
     <t>achievement+temp, overlaps=total_overlap for achievement might be useful, or just shift 1992 to the winning</t>
+  </si>
+  <si>
+    <t>axiom at least a few implies a few</t>
+  </si>
+  <si>
+    <t>CONSEQUENCE formulation is a bit strange… could take just the second part of the hypothesis</t>
+  </si>
+  <si>
+    <t>not entirely accurate as BEFORE is not direct precedence</t>
+  </si>
+  <si>
+    <t>modal…</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2379,8 +2397,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="40">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2574,12 +2598,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -2763,7 +2781,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
@@ -2772,7 +2790,8 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3150,13 +3169,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{184E8DB1-1DA0-4161-AC11-ADA355556CCF}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:P347"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="8" max="8" width="31.90625" customWidth="1"/>
-    <col min="11" max="11" width="54.08984375" customWidth="1"/>
+    <col min="8" max="8" width="31.85546875" customWidth="1"/>
+    <col min="11" max="11" width="54.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3185,7 +3204,7 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="K1" t="s">
         <v>9</v>
@@ -3197,7 +3216,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -3224,7 +3243,7 @@
         <v>17</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>18</v>
@@ -3238,7 +3257,7 @@
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
     </row>
-    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -3264,7 +3283,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -3290,7 +3309,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -3316,7 +3335,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -3345,7 +3364,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -3354,7 +3373,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -3383,7 +3402,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="L7">
         <v>1</v>
@@ -3392,7 +3411,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -3421,7 +3440,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="L8">
         <v>1</v>
@@ -3430,7 +3449,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -3459,7 +3478,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="L9">
         <v>1</v>
@@ -3468,7 +3487,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -3497,7 +3516,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="L10">
         <v>1</v>
@@ -3506,7 +3525,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -3535,7 +3554,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="L11">
         <v>1</v>
@@ -3544,7 +3563,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -3570,7 +3589,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -3605,7 +3624,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -3631,7 +3650,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -3657,7 +3676,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -3686,7 +3705,7 @@
         <v>1</v>
       </c>
       <c r="K16" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="L16">
         <v>1</v>
@@ -3695,7 +3714,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -3730,7 +3749,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -3759,7 +3778,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="L18">
         <v>1</v>
@@ -3768,7 +3787,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>12</v>
       </c>
@@ -3794,7 +3813,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -3820,7 +3839,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -3846,7 +3865,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -3872,7 +3891,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -3904,7 +3923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -3933,7 +3952,7 @@
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="L24">
         <v>1</v>
@@ -3942,7 +3961,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -3971,7 +3990,7 @@
         <v>1</v>
       </c>
       <c r="K25" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="L25">
         <v>1</v>
@@ -3980,7 +3999,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>12</v>
       </c>
@@ -4009,7 +4028,7 @@
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="L26">
         <v>1</v>
@@ -4018,7 +4037,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>12</v>
       </c>
@@ -4044,7 +4063,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>12</v>
       </c>
@@ -4070,7 +4089,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>12</v>
       </c>
@@ -4096,7 +4115,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>12</v>
       </c>
@@ -4125,7 +4144,7 @@
         <v>1</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="L30">
         <v>1</v>
@@ -4134,7 +4153,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>12</v>
       </c>
@@ -4166,7 +4185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>12</v>
       </c>
@@ -4195,7 +4214,7 @@
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="L32">
         <v>1</v>
@@ -4204,7 +4223,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>12</v>
       </c>
@@ -4233,7 +4252,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>12</v>
       </c>
@@ -4265,7 +4284,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>12</v>
       </c>
@@ -4291,7 +4310,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="36" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>12</v>
       </c>
@@ -4317,7 +4336,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>12</v>
       </c>
@@ -4343,7 +4362,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>12</v>
       </c>
@@ -4369,7 +4388,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>12</v>
       </c>
@@ -4398,7 +4417,7 @@
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="L39">
         <v>1</v>
@@ -4407,7 +4426,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>12</v>
       </c>
@@ -4439,7 +4458,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>12</v>
       </c>
@@ -4465,7 +4484,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="42" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>12</v>
       </c>
@@ -4491,7 +4510,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>12</v>
       </c>
@@ -4517,7 +4536,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>12</v>
       </c>
@@ -4543,7 +4562,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>12</v>
       </c>
@@ -4569,7 +4588,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>12</v>
       </c>
@@ -4595,7 +4614,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="47" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>12</v>
       </c>
@@ -4624,7 +4643,7 @@
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="L47">
         <v>2</v>
@@ -4633,7 +4652,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="48" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>12</v>
       </c>
@@ -4659,7 +4678,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>12</v>
       </c>
@@ -4688,7 +4707,7 @@
         <v>1</v>
       </c>
       <c r="K49" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="L49">
         <v>1</v>
@@ -4697,7 +4716,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="50" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>12</v>
       </c>
@@ -4723,7 +4742,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>12</v>
       </c>
@@ -4749,7 +4768,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>12</v>
       </c>
@@ -4775,7 +4794,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="53" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>12</v>
       </c>
@@ -4801,7 +4820,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="54" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>12</v>
       </c>
@@ -4827,7 +4846,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>12</v>
       </c>
@@ -4853,7 +4872,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="56" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>12</v>
       </c>
@@ -4888,7 +4907,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="57" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>12</v>
       </c>
@@ -4914,7 +4933,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="58" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>12</v>
       </c>
@@ -4949,7 +4968,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="59" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>12</v>
       </c>
@@ -4975,7 +4994,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="60" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>12</v>
       </c>
@@ -5000,17 +5019,17 @@
       <c r="I60" t="s">
         <v>17</v>
       </c>
-      <c r="J60" t="s">
-        <v>665</v>
+      <c r="J60">
+        <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>673</v>
+        <v>736</v>
       </c>
       <c r="M60" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="61" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>12</v>
       </c>
@@ -5036,7 +5055,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="62" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>12</v>
       </c>
@@ -5065,7 +5084,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="63" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>12</v>
       </c>
@@ -5094,7 +5113,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="64" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>12</v>
       </c>
@@ -5123,7 +5142,7 @@
         <v>1</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="L64">
         <v>1</v>
@@ -5132,7 +5151,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="65" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>12</v>
       </c>
@@ -5158,7 +5177,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="66" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>12</v>
       </c>
@@ -5184,7 +5203,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="67" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>12</v>
       </c>
@@ -5210,7 +5229,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="68" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>12</v>
       </c>
@@ -5236,7 +5255,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="69" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>12</v>
       </c>
@@ -5262,7 +5281,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="70" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>12</v>
       </c>
@@ -5288,7 +5307,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="71" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>12</v>
       </c>
@@ -5323,7 +5342,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="72" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>12</v>
       </c>
@@ -5349,7 +5368,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="73" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>12</v>
       </c>
@@ -5375,7 +5394,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="74" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>12</v>
       </c>
@@ -5401,7 +5420,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="75" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>12</v>
       </c>
@@ -5427,7 +5446,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>12</v>
       </c>
@@ -5453,7 +5472,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="77" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>12</v>
       </c>
@@ -5488,7 +5507,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="78" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>12</v>
       </c>
@@ -5517,7 +5536,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="79" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>12</v>
       </c>
@@ -5546,7 +5565,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="80" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>12</v>
       </c>
@@ -5572,7 +5591,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="81" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>12</v>
       </c>
@@ -5607,7 +5626,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="82" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>163</v>
       </c>
@@ -5642,7 +5661,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="83" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>163</v>
       </c>
@@ -5677,7 +5696,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="84" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>163</v>
       </c>
@@ -5703,7 +5722,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="85" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>163</v>
       </c>
@@ -5732,7 +5751,7 @@
         <v>1</v>
       </c>
       <c r="K85" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="L85">
         <v>1</v>
@@ -5741,7 +5760,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="86" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>163</v>
       </c>
@@ -5770,7 +5789,7 @@
         <v>1</v>
       </c>
       <c r="K86" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="L86">
         <v>1</v>
@@ -5779,7 +5798,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="87" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>163</v>
       </c>
@@ -5808,7 +5827,7 @@
         <v>1</v>
       </c>
       <c r="K87" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="L87">
         <v>1</v>
@@ -5817,7 +5836,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="88" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>163</v>
       </c>
@@ -5849,7 +5868,7 @@
         <v>1</v>
       </c>
       <c r="K88" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="L88">
         <v>1</v>
@@ -5858,7 +5877,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="89" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>163</v>
       </c>
@@ -5887,7 +5906,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="90" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>163</v>
       </c>
@@ -5916,7 +5935,7 @@
         <v>1</v>
       </c>
       <c r="K90" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="L90">
         <v>1</v>
@@ -5925,7 +5944,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="91" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>163</v>
       </c>
@@ -5954,7 +5973,7 @@
         <v>1</v>
       </c>
       <c r="K91" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="L91">
         <v>1</v>
@@ -5963,7 +5982,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="92" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>163</v>
       </c>
@@ -5989,7 +6008,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="93" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>163</v>
       </c>
@@ -6018,7 +6037,7 @@
         <v>1</v>
       </c>
       <c r="K93" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="L93">
         <v>1</v>
@@ -6027,7 +6046,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="94" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>163</v>
       </c>
@@ -6056,7 +6075,7 @@
         <v>1</v>
       </c>
       <c r="K94" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="L94">
         <v>1</v>
@@ -6065,7 +6084,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="95" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>163</v>
       </c>
@@ -6091,7 +6110,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="96" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>163</v>
       </c>
@@ -6117,7 +6136,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>163</v>
       </c>
@@ -6146,7 +6165,7 @@
         <v>1</v>
       </c>
       <c r="K97" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="L97">
         <v>1</v>
@@ -6155,7 +6174,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="98" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
         <v>163</v>
       </c>
@@ -6185,7 +6204,7 @@
         <v>1</v>
       </c>
       <c r="K98" s="3" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="L98" s="3">
         <v>1</v>
@@ -6196,7 +6215,7 @@
       <c r="N98" s="3"/>
       <c r="O98" s="3"/>
     </row>
-    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>163</v>
       </c>
@@ -6222,7 +6241,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="100" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>163</v>
       </c>
@@ -6248,7 +6267,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
         <v>163</v>
       </c>
@@ -6278,7 +6297,7 @@
         <v>1</v>
       </c>
       <c r="K101" s="3" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="L101" s="3">
         <v>1</v>
@@ -6289,7 +6308,7 @@
       <c r="N101" s="3"/>
       <c r="O101" s="3"/>
     </row>
-    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>163</v>
       </c>
@@ -6315,7 +6334,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>163</v>
       </c>
@@ -6341,7 +6360,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>163</v>
       </c>
@@ -6367,7 +6386,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>163</v>
       </c>
@@ -6393,7 +6412,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>163</v>
       </c>
@@ -6422,7 +6441,7 @@
         <v>1</v>
       </c>
       <c r="K106" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="L106">
         <v>1</v>
@@ -6431,7 +6450,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>163</v>
       </c>
@@ -6466,7 +6485,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>163</v>
       </c>
@@ -6492,7 +6511,7 @@
         <v>17</v>
       </c>
       <c r="J108" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="K108" t="s">
         <v>213</v>
@@ -6504,7 +6523,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>163</v>
       </c>
@@ -6530,7 +6549,7 @@
         <v>17</v>
       </c>
       <c r="J109" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="K109" t="s">
         <v>213</v>
@@ -6542,7 +6561,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>163</v>
       </c>
@@ -6574,7 +6593,7 @@
         <v>1</v>
       </c>
       <c r="K110" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="L110">
         <v>1</v>
@@ -6583,7 +6602,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="111" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>163</v>
       </c>
@@ -6618,7 +6637,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>163</v>
       </c>
@@ -6647,7 +6666,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="113" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>163</v>
       </c>
@@ -6676,7 +6695,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="114" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>163</v>
       </c>
@@ -6702,7 +6721,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>223</v>
       </c>
@@ -6731,7 +6750,7 @@
         <v>1</v>
       </c>
       <c r="K115" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="L115">
         <v>1</v>
@@ -6740,7 +6759,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="116" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>223</v>
       </c>
@@ -6769,7 +6788,7 @@
         <v>1</v>
       </c>
       <c r="K116" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="L116">
         <v>1</v>
@@ -6778,7 +6797,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>223</v>
       </c>
@@ -6807,16 +6826,16 @@
         <v>1</v>
       </c>
       <c r="K117" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="L117">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M117" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="118" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>223</v>
       </c>
@@ -6842,7 +6861,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="119" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>223</v>
       </c>
@@ -6868,7 +6887,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="120" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>223</v>
       </c>
@@ -6894,7 +6913,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="121" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>223</v>
       </c>
@@ -6920,7 +6939,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="122" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>223</v>
       </c>
@@ -6946,7 +6965,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="123" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>223</v>
       </c>
@@ -6972,7 +6991,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="124" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>223</v>
       </c>
@@ -6998,7 +7017,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="125" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>223</v>
       </c>
@@ -7024,7 +7043,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="126" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>223</v>
       </c>
@@ -7050,7 +7069,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="127" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>223</v>
       </c>
@@ -7076,7 +7095,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="128" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>223</v>
       </c>
@@ -7105,7 +7124,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="129" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>223</v>
       </c>
@@ -7131,7 +7150,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="130" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>223</v>
       </c>
@@ -7160,7 +7179,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="131" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>223</v>
       </c>
@@ -7189,7 +7208,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="132" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>223</v>
       </c>
@@ -7215,7 +7234,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="133" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>223</v>
       </c>
@@ -7241,7 +7260,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="134" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>223</v>
       </c>
@@ -7267,7 +7286,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="135" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>223</v>
       </c>
@@ -7293,7 +7312,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="136" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>223</v>
       </c>
@@ -7319,7 +7338,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="137" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>223</v>
       </c>
@@ -7345,7 +7364,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="138" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>223</v>
       </c>
@@ -7371,7 +7390,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="139" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>223</v>
       </c>
@@ -7397,7 +7416,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="140" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>223</v>
       </c>
@@ -7435,7 +7454,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="141" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>223</v>
       </c>
@@ -7464,7 +7483,7 @@
         <v>1</v>
       </c>
       <c r="K141" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="L141">
         <v>1</v>
@@ -7473,7 +7492,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="142" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>223</v>
       </c>
@@ -7499,7 +7518,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="143" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>279</v>
       </c>
@@ -7525,7 +7544,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="144" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>279</v>
       </c>
@@ -7551,7 +7570,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="145" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>279</v>
       </c>
@@ -7577,7 +7596,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="146" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>279</v>
       </c>
@@ -7603,7 +7622,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="147" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>279</v>
       </c>
@@ -7629,7 +7648,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="148" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>279</v>
       </c>
@@ -7655,7 +7674,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="149" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>279</v>
       </c>
@@ -7681,7 +7700,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="150" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>279</v>
       </c>
@@ -7707,7 +7726,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="151" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>279</v>
       </c>
@@ -7736,7 +7755,7 @@
         <v>1</v>
       </c>
       <c r="K151" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="L151">
         <v>1</v>
@@ -7745,7 +7764,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="152" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>279</v>
       </c>
@@ -7774,7 +7793,7 @@
         <v>1</v>
       </c>
       <c r="K152" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="L152">
         <v>1</v>
@@ -7783,7 +7802,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="153" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>279</v>
       </c>
@@ -7812,7 +7831,7 @@
         <v>1</v>
       </c>
       <c r="K153" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="L153">
         <v>1</v>
@@ -7821,7 +7840,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="154" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>279</v>
       </c>
@@ -7850,7 +7869,7 @@
         <v>1</v>
       </c>
       <c r="K154" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="L154">
         <v>1</v>
@@ -7859,7 +7878,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="155" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>279</v>
       </c>
@@ -7885,7 +7904,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="156" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>279</v>
       </c>
@@ -7911,7 +7930,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="157" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>279</v>
       </c>
@@ -7937,7 +7956,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="158" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>279</v>
       </c>
@@ -7963,7 +7982,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="159" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>279</v>
       </c>
@@ -7989,7 +8008,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="160" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>279</v>
       </c>
@@ -8015,7 +8034,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="161" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>279</v>
       </c>
@@ -8044,7 +8063,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="162" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>279</v>
       </c>
@@ -8073,7 +8092,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="163" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>279</v>
       </c>
@@ -8099,7 +8118,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="164" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>279</v>
       </c>
@@ -8125,7 +8144,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="165" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>279</v>
       </c>
@@ -8151,7 +8170,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="166" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>279</v>
       </c>
@@ -8177,7 +8196,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="167" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>279</v>
       </c>
@@ -8203,7 +8222,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="168" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>279</v>
       </c>
@@ -8229,7 +8248,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="169" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>279</v>
       </c>
@@ -8255,7 +8274,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="170" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>279</v>
       </c>
@@ -8287,7 +8306,7 @@
         <v>1</v>
       </c>
       <c r="K170" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="L170">
         <v>1</v>
@@ -8296,7 +8315,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="171" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>279</v>
       </c>
@@ -8328,7 +8347,7 @@
         <v>1</v>
       </c>
       <c r="K171" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="L171">
         <v>1</v>
@@ -8337,7 +8356,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="172" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>279</v>
       </c>
@@ -8363,7 +8382,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="173" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>279</v>
       </c>
@@ -8389,7 +8408,7 @@
         <v>17</v>
       </c>
       <c r="J173" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="K173" t="s">
         <v>340</v>
@@ -8401,7 +8420,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="174" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>279</v>
       </c>
@@ -8427,7 +8446,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="175" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>279</v>
       </c>
@@ -8453,7 +8472,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="176" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>279</v>
       </c>
@@ -8485,7 +8504,7 @@
         <v>1</v>
       </c>
       <c r="K176" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="L176">
         <v>1</v>
@@ -8494,7 +8513,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="177" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>279</v>
       </c>
@@ -8526,7 +8545,7 @@
         <v>1</v>
       </c>
       <c r="K177" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="L177">
         <v>1</v>
@@ -8535,7 +8554,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="178" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>279</v>
       </c>
@@ -8561,7 +8580,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="179" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>279</v>
       </c>
@@ -8590,7 +8609,7 @@
         <v>1</v>
       </c>
       <c r="K179" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="L179">
         <v>1</v>
@@ -8599,7 +8618,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="180" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>279</v>
       </c>
@@ -8625,7 +8644,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="181" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>279</v>
       </c>
@@ -8655,7 +8674,7 @@
         <v>1</v>
       </c>
       <c r="K181" s="2" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="L181" s="2">
         <v>1</v>
@@ -8666,7 +8685,7 @@
       <c r="N181" s="2"/>
       <c r="O181" s="2"/>
     </row>
-    <row r="182" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>279</v>
       </c>
@@ -8692,7 +8711,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="183" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>279</v>
       </c>
@@ -8730,7 +8749,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="184" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>279</v>
       </c>
@@ -8762,7 +8781,7 @@
         <v>1</v>
       </c>
       <c r="K184" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="L184">
         <v>1</v>
@@ -8771,7 +8790,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="185" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>279</v>
       </c>
@@ -8797,7 +8816,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="186" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>279</v>
       </c>
@@ -8835,7 +8854,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="187" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>279</v>
       </c>
@@ -8867,7 +8886,7 @@
         <v>1</v>
       </c>
       <c r="K187" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="L187">
         <v>1</v>
@@ -8876,7 +8895,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="188" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>279</v>
       </c>
@@ -8914,7 +8933,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="189" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>279</v>
       </c>
@@ -8940,7 +8959,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="190" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>279</v>
       </c>
@@ -8969,7 +8988,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="191" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>279</v>
       </c>
@@ -8998,7 +9017,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="192" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>279</v>
       </c>
@@ -9023,11 +9042,11 @@
       <c r="I192" t="s">
         <v>17</v>
       </c>
-      <c r="J192" t="s">
-        <v>665</v>
+      <c r="J192">
+        <v>1</v>
       </c>
       <c r="K192" t="s">
-        <v>340</v>
+        <v>737</v>
       </c>
       <c r="L192">
         <v>1</v>
@@ -9036,7 +9055,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="193" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>279</v>
       </c>
@@ -9062,7 +9081,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="194" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>279</v>
       </c>
@@ -9087,11 +9106,11 @@
       <c r="I194" t="s">
         <v>17</v>
       </c>
-      <c r="J194" t="s">
-        <v>665</v>
+      <c r="J194">
+        <v>1</v>
       </c>
       <c r="K194" t="s">
-        <v>340</v>
+        <v>737</v>
       </c>
       <c r="L194">
         <v>1</v>
@@ -9100,7 +9119,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="195" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>279</v>
       </c>
@@ -9126,7 +9145,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="196" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>279</v>
       </c>
@@ -9151,11 +9170,11 @@
       <c r="I196" t="s">
         <v>17</v>
       </c>
-      <c r="J196" t="s">
-        <v>665</v>
+      <c r="J196">
+        <v>1</v>
       </c>
       <c r="K196" t="s">
-        <v>340</v>
+        <v>737</v>
       </c>
       <c r="L196">
         <v>1</v>
@@ -9164,7 +9183,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="197" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>279</v>
       </c>
@@ -9190,7 +9209,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="198" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>386</v>
       </c>
@@ -9225,7 +9244,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="199" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>386</v>
       </c>
@@ -9257,7 +9276,7 @@
         <v>1</v>
       </c>
       <c r="K199" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="L199">
         <v>2</v>
@@ -9266,7 +9285,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="200" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>386</v>
       </c>
@@ -9298,7 +9317,7 @@
         <v>1</v>
       </c>
       <c r="K200" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="L200">
         <v>2</v>
@@ -9307,7 +9326,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="201" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>386</v>
       </c>
@@ -9333,7 +9352,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="202" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>386</v>
       </c>
@@ -9359,7 +9378,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="203" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>386</v>
       </c>
@@ -9394,7 +9413,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="204" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>386</v>
       </c>
@@ -9429,7 +9448,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="205" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>386</v>
       </c>
@@ -9467,7 +9486,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="206" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>386</v>
       </c>
@@ -9505,7 +9524,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="207" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>386</v>
       </c>
@@ -9531,7 +9550,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="208" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>386</v>
       </c>
@@ -9557,7 +9576,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="209" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>386</v>
       </c>
@@ -9583,7 +9602,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="210" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>386</v>
       </c>
@@ -9609,7 +9628,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="211" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>386</v>
       </c>
@@ -9635,7 +9654,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="212" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>386</v>
       </c>
@@ -9661,7 +9680,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="213" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>386</v>
       </c>
@@ -9687,7 +9706,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="214" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>386</v>
       </c>
@@ -9716,7 +9735,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="215" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>386</v>
       </c>
@@ -9742,7 +9761,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="216" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>386</v>
       </c>
@@ -9768,7 +9787,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="217" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="3" t="s">
         <v>386</v>
       </c>
@@ -9795,7 +9814,7 @@
         <v>17</v>
       </c>
       <c r="J217" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="K217" s="3"/>
       <c r="L217" s="3">
@@ -9807,7 +9826,7 @@
       <c r="N217" s="3"/>
       <c r="O217" s="3"/>
     </row>
-    <row r="218" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>386</v>
       </c>
@@ -9833,7 +9852,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="219" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>386</v>
       </c>
@@ -9862,7 +9881,7 @@
         <v>1</v>
       </c>
       <c r="K219" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="L219">
         <v>1</v>
@@ -9871,7 +9890,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="220" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>386</v>
       </c>
@@ -9897,7 +9916,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="221" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>434</v>
       </c>
@@ -9923,7 +9942,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="222" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>434</v>
       </c>
@@ -9949,7 +9968,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="223" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>434</v>
       </c>
@@ -9975,7 +9994,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="224" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>434</v>
       </c>
@@ -10001,7 +10020,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="225" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>434</v>
       </c>
@@ -10027,7 +10046,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="226" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>434</v>
       </c>
@@ -10053,7 +10072,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="227" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>434</v>
       </c>
@@ -10079,7 +10098,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="228" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>434</v>
       </c>
@@ -10105,7 +10124,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="229" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>434</v>
       </c>
@@ -10131,7 +10150,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="230" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="3" t="s">
         <v>434</v>
       </c>
@@ -10158,7 +10177,7 @@
         <v>31</v>
       </c>
       <c r="J230" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="K230" s="3" t="s">
         <v>405</v>
@@ -10172,7 +10191,7 @@
       <c r="N230" s="3"/>
       <c r="O230" s="3"/>
     </row>
-    <row r="231" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="3" t="s">
         <v>434</v>
       </c>
@@ -10199,7 +10218,7 @@
         <v>17</v>
       </c>
       <c r="J231" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="K231" s="3"/>
       <c r="L231" s="3">
@@ -10211,7 +10230,7 @@
       <c r="N231" s="3"/>
       <c r="O231" s="3"/>
     </row>
-    <row r="232" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>434</v>
       </c>
@@ -10237,7 +10256,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="233" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>434</v>
       </c>
@@ -10263,7 +10282,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="234" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="3" t="s">
         <v>434</v>
       </c>
@@ -10290,7 +10309,7 @@
         <v>17</v>
       </c>
       <c r="J234" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="K234" s="3"/>
       <c r="L234" s="3">
@@ -10302,7 +10321,7 @@
       <c r="N234" s="3"/>
       <c r="O234" s="3"/>
     </row>
-    <row r="235" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>434</v>
       </c>
@@ -10328,7 +10347,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="236" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>434</v>
       </c>
@@ -10354,7 +10373,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="237" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="3" t="s">
         <v>434</v>
       </c>
@@ -10381,7 +10400,7 @@
         <v>17</v>
       </c>
       <c r="J237" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="K237" s="3" t="s">
         <v>456</v>
@@ -10395,7 +10414,7 @@
       <c r="N237" s="3"/>
       <c r="O237" s="3"/>
     </row>
-    <row r="238" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="3" t="s">
         <v>434</v>
       </c>
@@ -10422,7 +10441,7 @@
         <v>17</v>
       </c>
       <c r="J238" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="K238" s="3" t="s">
         <v>456</v>
@@ -10436,7 +10455,7 @@
       <c r="N238" s="3"/>
       <c r="O238" s="3"/>
     </row>
-    <row r="239" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>434</v>
       </c>
@@ -10462,7 +10481,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="240" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="3" t="s">
         <v>434</v>
       </c>
@@ -10489,7 +10508,7 @@
         <v>17</v>
       </c>
       <c r="J240" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="K240" s="3"/>
       <c r="L240" s="3">
@@ -10501,7 +10520,7 @@
       <c r="N240" s="3"/>
       <c r="O240" s="3"/>
     </row>
-    <row r="241" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>434</v>
       </c>
@@ -10527,7 +10546,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="242" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>434</v>
       </c>
@@ -10553,7 +10572,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="243" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>434</v>
       </c>
@@ -10579,7 +10598,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="244" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>434</v>
       </c>
@@ -10605,7 +10624,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="245" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="3" t="s">
         <v>434</v>
       </c>
@@ -10634,7 +10653,7 @@
         <v>473</v>
       </c>
       <c r="J245" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="K245" s="3"/>
       <c r="L245" s="3">
@@ -10646,7 +10665,7 @@
       <c r="N245" s="3"/>
       <c r="O245" s="3"/>
     </row>
-    <row r="246" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="3" t="s">
         <v>434</v>
       </c>
@@ -10675,7 +10694,7 @@
         <v>473</v>
       </c>
       <c r="J246" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="K246" s="3"/>
       <c r="L246" s="3">
@@ -10687,7 +10706,7 @@
       <c r="N246" s="3"/>
       <c r="O246" s="3"/>
     </row>
-    <row r="247" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>434</v>
       </c>
@@ -10713,7 +10732,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="248" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>434</v>
       </c>
@@ -10739,7 +10758,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="249" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>434</v>
       </c>
@@ -10765,7 +10784,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="250" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="3" t="s">
         <v>434</v>
       </c>
@@ -10792,7 +10811,7 @@
         <v>17</v>
       </c>
       <c r="J250" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="K250" s="3"/>
       <c r="L250" s="3">
@@ -10804,7 +10823,7 @@
       <c r="N250" s="3"/>
       <c r="O250" s="3"/>
     </row>
-    <row r="251" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="3" t="s">
         <v>434</v>
       </c>
@@ -10833,7 +10852,7 @@
         <v>473</v>
       </c>
       <c r="J251" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="K251" s="3"/>
       <c r="L251" s="3">
@@ -10845,7 +10864,7 @@
       <c r="N251" s="3"/>
       <c r="O251" s="3"/>
     </row>
-    <row r="252" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>481</v>
       </c>
@@ -10883,7 +10902,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="253" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>481</v>
       </c>
@@ -10909,7 +10928,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="254" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>481</v>
       </c>
@@ -10935,7 +10954,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="255" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>481</v>
       </c>
@@ -10961,7 +10980,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="256" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>481</v>
       </c>
@@ -10987,7 +11006,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="257" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>481</v>
       </c>
@@ -11016,7 +11035,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="258" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>481</v>
       </c>
@@ -11045,48 +11064,48 @@
         <v>473</v>
       </c>
     </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A259" s="6" t="s">
+    <row r="259" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A259" s="5" t="s">
         <v>481</v>
       </c>
-      <c r="B259" s="6" t="s">
+      <c r="B259" s="5" t="s">
         <v>482</v>
       </c>
-      <c r="C259" s="6">
+      <c r="C259" s="5">
         <v>258</v>
       </c>
-      <c r="D259" s="6" t="s">
+      <c r="D259" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E259" s="6"/>
-      <c r="F259" s="6">
-        <v>0</v>
-      </c>
-      <c r="G259" s="6" t="s">
+      <c r="E259" s="5"/>
+      <c r="F259" s="5">
+        <v>0</v>
+      </c>
+      <c r="G259" s="5" t="s">
         <v>496</v>
       </c>
-      <c r="H259" s="6" t="s">
+      <c r="H259" s="5" t="s">
         <v>497</v>
       </c>
-      <c r="I259" s="6" t="s">
+      <c r="I259" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="J259" s="6" t="s">
-        <v>695</v>
-      </c>
-      <c r="K259" s="6" t="s">
-        <v>716</v>
-      </c>
-      <c r="L259" s="6">
+      <c r="J259" s="5" t="s">
+        <v>693</v>
+      </c>
+      <c r="K259" s="5" t="s">
+        <v>714</v>
+      </c>
+      <c r="L259" s="5">
         <v>2</v>
       </c>
-      <c r="M259" s="6" t="s">
+      <c r="M259" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="N259" s="6"/>
-      <c r="O259" s="6"/>
-    </row>
-    <row r="260" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="N259" s="5"/>
+      <c r="O259" s="5"/>
+    </row>
+    <row r="260" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>481</v>
       </c>
@@ -11112,7 +11131,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="261" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>481</v>
       </c>
@@ -11138,7 +11157,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="262" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>481</v>
       </c>
@@ -11164,7 +11183,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="263" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>481</v>
       </c>
@@ -11190,7 +11209,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="264" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>481</v>
       </c>
@@ -11216,7 +11235,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="265" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>481</v>
       </c>
@@ -11242,7 +11261,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="266" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>481</v>
       </c>
@@ -11268,7 +11287,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="267" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>481</v>
       </c>
@@ -11294,7 +11313,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="268" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>481</v>
       </c>
@@ -11320,7 +11339,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="269" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>481</v>
       </c>
@@ -11346,7 +11365,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="270" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>481</v>
       </c>
@@ -11372,7 +11391,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="271" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>481</v>
       </c>
@@ -11398,7 +11417,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="272" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>481</v>
       </c>
@@ -11424,7 +11443,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="273" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>481</v>
       </c>
@@ -11450,7 +11469,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="274" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>481</v>
       </c>
@@ -11476,7 +11495,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="275" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>481</v>
       </c>
@@ -11502,7 +11521,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="276" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>481</v>
       </c>
@@ -11528,7 +11547,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="277" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>481</v>
       </c>
@@ -11551,7 +11570,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="278" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>481</v>
       </c>
@@ -11577,7 +11596,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>481</v>
       </c>
@@ -11603,10 +11622,10 @@
         <v>31</v>
       </c>
       <c r="J279" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="K279" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="L279">
         <v>2</v>
@@ -11615,7 +11634,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>481</v>
       </c>
@@ -11641,10 +11660,10 @@
         <v>31</v>
       </c>
       <c r="J280" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="K280" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="L280">
         <v>1</v>
@@ -11653,7 +11672,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="281" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>481</v>
       </c>
@@ -11679,7 +11698,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="282" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>481</v>
       </c>
@@ -11705,7 +11724,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="283" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>481</v>
       </c>
@@ -11731,10 +11750,10 @@
         <v>31</v>
       </c>
       <c r="J283" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="K283" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="L283">
         <v>1</v>
@@ -11743,7 +11762,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="284" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>481</v>
       </c>
@@ -11769,7 +11788,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="285" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>481</v>
       </c>
@@ -11795,7 +11814,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="286" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>481</v>
       </c>
@@ -11821,7 +11840,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="287" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>481</v>
       </c>
@@ -11847,10 +11866,10 @@
         <v>31</v>
       </c>
       <c r="J287" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="K287" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="L287">
         <v>1</v>
@@ -11859,7 +11878,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="288" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>481</v>
       </c>
@@ -11885,7 +11904,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="289" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>481</v>
       </c>
@@ -11911,10 +11930,10 @@
         <v>17</v>
       </c>
       <c r="J289" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="K289" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="L289">
         <v>1</v>
@@ -11923,49 +11942,49 @@
         <v>554</v>
       </c>
     </row>
-    <row r="290" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A290" s="5" t="s">
+    <row r="290" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A290" s="4" t="s">
         <v>481</v>
       </c>
-      <c r="B290" s="5" t="s">
+      <c r="B290" s="4" t="s">
         <v>498</v>
       </c>
-      <c r="C290" s="5">
+      <c r="C290" s="4">
         <v>289</v>
       </c>
-      <c r="D290" s="5" t="s">
+      <c r="D290" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E290" s="5"/>
-      <c r="F290" s="5">
-        <v>0</v>
-      </c>
-      <c r="G290" s="5" t="s">
+      <c r="E290" s="4"/>
+      <c r="F290" s="4">
+        <v>0</v>
+      </c>
+      <c r="G290" s="4" t="s">
         <v>555</v>
       </c>
-      <c r="H290" s="5" t="s">
+      <c r="H290" s="4" t="s">
         <v>556</v>
       </c>
-      <c r="I290" s="5" t="s">
+      <c r="I290" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="J290" s="5" t="s">
-        <v>695</v>
-      </c>
-      <c r="K290" s="5" t="s">
-        <v>722</v>
-      </c>
-      <c r="L290" s="5">
-        <v>1</v>
-      </c>
-      <c r="M290" s="5" t="s">
+      <c r="J290" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="K290" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="L290" s="4">
+        <v>1</v>
+      </c>
+      <c r="M290" s="4" t="s">
         <v>551</v>
       </c>
-      <c r="N290" s="5"/>
-      <c r="O290" s="5"/>
-      <c r="P290" s="5"/>
-    </row>
-    <row r="291" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="N290" s="4"/>
+      <c r="O290" s="4"/>
+      <c r="P290" s="4"/>
+    </row>
+    <row r="291" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>481</v>
       </c>
@@ -11991,10 +12010,10 @@
         <v>17</v>
       </c>
       <c r="J291" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="K291" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="L291">
         <v>1</v>
@@ -12003,7 +12022,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="292" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A292" s="3" t="s">
         <v>481</v>
       </c>
@@ -12032,10 +12051,10 @@
         <v>560</v>
       </c>
       <c r="J292" s="3" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="K292" s="3" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="L292" s="3">
         <v>1</v>
@@ -12046,7 +12065,7 @@
       <c r="N292" s="3"/>
       <c r="O292" s="3"/>
     </row>
-    <row r="293" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>481</v>
       </c>
@@ -12072,7 +12091,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="294" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>481</v>
       </c>
@@ -12098,7 +12117,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="295" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>481</v>
       </c>
@@ -12124,10 +12143,10 @@
         <v>17</v>
       </c>
       <c r="J295" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="K295" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="L295">
         <v>1</v>
@@ -12136,7 +12155,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="296" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>481</v>
       </c>
@@ -12162,7 +12181,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="297" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>481</v>
       </c>
@@ -12188,7 +12207,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="298" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>481</v>
       </c>
@@ -12214,10 +12233,10 @@
         <v>17</v>
       </c>
       <c r="J298" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="K298" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="L298">
         <v>1</v>
@@ -12226,7 +12245,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="299" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>481</v>
       </c>
@@ -12252,10 +12271,10 @@
         <v>17</v>
       </c>
       <c r="J299" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="K299" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="L299">
         <v>1</v>
@@ -12264,7 +12283,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="300" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>481</v>
       </c>
@@ -12290,10 +12309,10 @@
         <v>31</v>
       </c>
       <c r="J300" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="K300" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="L300">
         <v>1</v>
@@ -12302,7 +12321,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="301" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>481</v>
       </c>
@@ -12328,10 +12347,10 @@
         <v>17</v>
       </c>
       <c r="J301" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="K301" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="L301">
         <v>1</v>
@@ -12340,7 +12359,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="302" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>481</v>
       </c>
@@ -12366,10 +12385,10 @@
         <v>17</v>
       </c>
       <c r="J302" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="K302" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="L302">
         <v>1</v>
@@ -12378,7 +12397,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="303" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>481</v>
       </c>
@@ -12404,10 +12423,10 @@
         <v>17</v>
       </c>
       <c r="J303" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="K303" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="L303">
         <v>1</v>
@@ -12416,7 +12435,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="304" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>481</v>
       </c>
@@ -12442,10 +12461,10 @@
         <v>17</v>
       </c>
       <c r="J304" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="K304" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="L304">
         <v>1</v>
@@ -12454,7 +12473,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="305" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>481</v>
       </c>
@@ -12480,7 +12499,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="306" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>481</v>
       </c>
@@ -12503,7 +12522,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="307" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A307" s="3" t="s">
         <v>481</v>
       </c>
@@ -12530,10 +12549,10 @@
         <v>17</v>
       </c>
       <c r="J307" s="3" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="K307" s="3" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="L307" s="3">
         <v>1</v>
@@ -12544,7 +12563,7 @@
       <c r="N307" s="3"/>
       <c r="O307" s="3"/>
     </row>
-    <row r="308" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>481</v>
       </c>
@@ -12570,10 +12589,10 @@
         <v>17</v>
       </c>
       <c r="J308" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="K308" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="L308">
         <v>1</v>
@@ -12582,7 +12601,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="309" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>481</v>
       </c>
@@ -12611,7 +12630,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="310" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>481</v>
       </c>
@@ -12634,7 +12653,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="311" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>481</v>
       </c>
@@ -12657,7 +12676,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="312" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>481</v>
       </c>
@@ -12683,7 +12702,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="313" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>481</v>
       </c>
@@ -12709,7 +12728,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="314" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>481</v>
       </c>
@@ -12735,7 +12754,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="315" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>481</v>
       </c>
@@ -12761,7 +12780,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="316" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>481</v>
       </c>
@@ -12786,20 +12805,20 @@
       <c r="I316" t="s">
         <v>17</v>
       </c>
-      <c r="J316" s="4" t="s">
-        <v>696</v>
+      <c r="J316" s="9">
+        <v>1</v>
       </c>
       <c r="K316" t="s">
-        <v>601</v>
+        <v>738</v>
       </c>
       <c r="L316">
         <v>2</v>
       </c>
       <c r="M316" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="317" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="317" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>481</v>
       </c>
@@ -12816,16 +12835,16 @@
         <v>1</v>
       </c>
       <c r="G317" t="s">
+        <v>602</v>
+      </c>
+      <c r="H317" t="s">
         <v>603</v>
       </c>
-      <c r="H317" t="s">
-        <v>604</v>
-      </c>
       <c r="I317" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="318" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>481</v>
       </c>
@@ -12842,16 +12861,16 @@
         <v>1</v>
       </c>
       <c r="G318" t="s">
+        <v>604</v>
+      </c>
+      <c r="H318" t="s">
         <v>605</v>
       </c>
-      <c r="H318" t="s">
-        <v>606</v>
-      </c>
       <c r="I318" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="319" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>481</v>
       </c>
@@ -12868,16 +12887,16 @@
         <v>1</v>
       </c>
       <c r="G319" t="s">
+        <v>606</v>
+      </c>
+      <c r="H319" t="s">
         <v>607</v>
-      </c>
-      <c r="H319" t="s">
-        <v>608</v>
       </c>
       <c r="I319" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="320" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>481</v>
       </c>
@@ -12894,16 +12913,16 @@
         <v>1</v>
       </c>
       <c r="G320" t="s">
+        <v>608</v>
+      </c>
+      <c r="H320" t="s">
         <v>609</v>
       </c>
-      <c r="H320" t="s">
-        <v>610</v>
-      </c>
       <c r="I320" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="321" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>481</v>
       </c>
@@ -12920,28 +12939,28 @@
         <v>0</v>
       </c>
       <c r="G321" t="s">
+        <v>610</v>
+      </c>
+      <c r="H321" t="s">
         <v>611</v>
       </c>
-      <c r="H321" t="s">
-        <v>612</v>
-      </c>
       <c r="I321" t="s">
         <v>17</v>
       </c>
-      <c r="J321" s="4" t="s">
-        <v>696</v>
+      <c r="J321" s="8" t="s">
+        <v>694</v>
       </c>
       <c r="K321" t="s">
-        <v>601</v>
+        <v>739</v>
       </c>
       <c r="L321">
         <v>2</v>
       </c>
       <c r="M321" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="322" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="322" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>481</v>
       </c>
@@ -12958,16 +12977,16 @@
         <v>1</v>
       </c>
       <c r="G322" t="s">
+        <v>613</v>
+      </c>
+      <c r="H322" t="s">
         <v>614</v>
       </c>
-      <c r="H322" t="s">
-        <v>615</v>
-      </c>
       <c r="I322" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="323" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>481</v>
       </c>
@@ -12984,28 +13003,28 @@
         <v>0</v>
       </c>
       <c r="G323" t="s">
+        <v>615</v>
+      </c>
+      <c r="H323" t="s">
         <v>616</v>
       </c>
-      <c r="H323" t="s">
-        <v>617</v>
-      </c>
       <c r="I323" t="s">
         <v>17</v>
       </c>
-      <c r="J323" s="4" t="s">
-        <v>696</v>
+      <c r="J323" s="8" t="s">
+        <v>694</v>
       </c>
       <c r="K323" t="s">
-        <v>601</v>
+        <v>739</v>
       </c>
       <c r="L323">
         <v>2</v>
       </c>
       <c r="M323" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="324" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="324" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>481</v>
       </c>
@@ -13022,16 +13041,16 @@
         <v>1</v>
       </c>
       <c r="G324" t="s">
+        <v>618</v>
+      </c>
+      <c r="H324" t="s">
         <v>619</v>
       </c>
-      <c r="H324" t="s">
-        <v>620</v>
-      </c>
       <c r="I324" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="325" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>481</v>
       </c>
@@ -13048,28 +13067,28 @@
         <v>0</v>
       </c>
       <c r="G325" t="s">
+        <v>620</v>
+      </c>
+      <c r="H325" t="s">
         <v>621</v>
       </c>
-      <c r="H325" t="s">
-        <v>622</v>
-      </c>
       <c r="I325" t="s">
         <v>17</v>
       </c>
-      <c r="J325" s="4" t="s">
-        <v>696</v>
+      <c r="J325" s="8" t="s">
+        <v>694</v>
       </c>
       <c r="K325" t="s">
-        <v>405</v>
+        <v>739</v>
       </c>
       <c r="L325">
         <v>2</v>
       </c>
       <c r="M325" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="326" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="326" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>481</v>
       </c>
@@ -13086,62 +13105,62 @@
         <v>1</v>
       </c>
       <c r="G326" t="s">
+        <v>623</v>
+      </c>
+      <c r="H326" t="s">
         <v>624</v>
       </c>
-      <c r="H326" t="s">
+      <c r="I326" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="327" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A327" s="4" t="s">
         <v>625</v>
       </c>
-      <c r="I326" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="327" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A327" s="5" t="s">
+      <c r="B327" s="4" t="s">
         <v>626</v>
       </c>
-      <c r="B327" s="5" t="s">
+      <c r="C327" s="4">
+        <v>326</v>
+      </c>
+      <c r="D327" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E327" s="4"/>
+      <c r="F327" s="4">
+        <v>0</v>
+      </c>
+      <c r="G327" s="4" t="s">
         <v>627</v>
       </c>
-      <c r="C327" s="5">
-        <v>326</v>
-      </c>
-      <c r="D327" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E327" s="5"/>
-      <c r="F327" s="5">
-        <v>0</v>
-      </c>
-      <c r="G327" s="5" t="s">
+      <c r="H327" s="4" t="s">
         <v>628</v>
       </c>
-      <c r="H327" s="5" t="s">
-        <v>629</v>
-      </c>
-      <c r="I327" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J327" s="5" t="s">
-        <v>695</v>
-      </c>
-      <c r="K327" s="5" t="s">
-        <v>733</v>
-      </c>
-      <c r="L327" s="5">
+      <c r="I327" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J327" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="K327" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="L327" s="4">
         <v>2</v>
       </c>
-      <c r="M327" s="5" t="s">
+      <c r="M327" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="N327" s="5"/>
-      <c r="O327" s="5"/>
-    </row>
-    <row r="328" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="N327" s="4"/>
+      <c r="O327" s="4"/>
+    </row>
+    <row r="328" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
+        <v>625</v>
+      </c>
+      <c r="B328" t="s">
         <v>626</v>
-      </c>
-      <c r="B328" t="s">
-        <v>627</v>
       </c>
       <c r="C328">
         <v>327</v>
@@ -13153,21 +13172,21 @@
         <v>0</v>
       </c>
       <c r="G328" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H328" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="I328" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="329" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
+        <v>625</v>
+      </c>
+      <c r="B329" t="s">
         <v>626</v>
-      </c>
-      <c r="B329" t="s">
-        <v>627</v>
       </c>
       <c r="C329">
         <v>328</v>
@@ -13179,19 +13198,19 @@
         <v>0</v>
       </c>
       <c r="G329" t="s">
+        <v>630</v>
+      </c>
+      <c r="H329" t="s">
         <v>631</v>
       </c>
-      <c r="H329" t="s">
-        <v>632</v>
-      </c>
       <c r="I329" t="s">
         <v>17</v>
       </c>
       <c r="J329" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="K329" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="L329">
         <v>1</v>
@@ -13200,12 +13219,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="330" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
+        <v>625</v>
+      </c>
+      <c r="B330" t="s">
         <v>626</v>
-      </c>
-      <c r="B330" t="s">
-        <v>627</v>
       </c>
       <c r="C330">
         <v>329</v>
@@ -13217,62 +13236,62 @@
         <v>0</v>
       </c>
       <c r="G330" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H330" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="I330" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="331" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A331" s="6" t="s">
+    <row r="331" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A331" s="5" t="s">
+        <v>625</v>
+      </c>
+      <c r="B331" s="5" t="s">
         <v>626</v>
       </c>
-      <c r="B331" s="6" t="s">
-        <v>627</v>
-      </c>
-      <c r="C331" s="6">
+      <c r="C331" s="5">
         <v>330</v>
       </c>
-      <c r="D331" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E331" s="6"/>
-      <c r="F331" s="6">
-        <v>0</v>
-      </c>
-      <c r="G331" s="6" t="s">
+      <c r="D331" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E331" s="5"/>
+      <c r="F331" s="5">
+        <v>0</v>
+      </c>
+      <c r="G331" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="H331" s="5" t="s">
         <v>634</v>
       </c>
-      <c r="H331" s="6" t="s">
+      <c r="I331" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J331" s="5" t="s">
+        <v>693</v>
+      </c>
+      <c r="K331" s="5" t="s">
+        <v>733</v>
+      </c>
+      <c r="L331" s="5">
+        <v>2</v>
+      </c>
+      <c r="M331" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="N331" s="5"/>
+      <c r="O331" s="5"/>
+    </row>
+    <row r="332" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A332" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="B332" s="3" t="s">
         <v>635</v>
-      </c>
-      <c r="I331" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="J331" s="6" t="s">
-        <v>695</v>
-      </c>
-      <c r="K331" s="6" t="s">
-        <v>735</v>
-      </c>
-      <c r="L331" s="6">
-        <v>2</v>
-      </c>
-      <c r="M331" s="6" t="s">
-        <v>554</v>
-      </c>
-      <c r="N331" s="6"/>
-      <c r="O331" s="6"/>
-    </row>
-    <row r="332" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A332" s="3" t="s">
-        <v>626</v>
-      </c>
-      <c r="B332" s="3" t="s">
-        <v>636</v>
       </c>
       <c r="C332" s="3">
         <v>331</v>
@@ -13285,35 +13304,35 @@
         <v>0</v>
       </c>
       <c r="G332" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="H332" s="3" t="s">
         <v>637</v>
       </c>
-      <c r="H332" s="3" t="s">
+      <c r="I332" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J332" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="K332" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="L332" s="3">
+        <v>1</v>
+      </c>
+      <c r="M332" s="3" t="s">
         <v>638</v>
-      </c>
-      <c r="I332" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J332" s="3" t="s">
-        <v>695</v>
-      </c>
-      <c r="K332" s="3" t="s">
-        <v>697</v>
-      </c>
-      <c r="L332" s="3">
-        <v>1</v>
-      </c>
-      <c r="M332" s="3" t="s">
-        <v>639</v>
       </c>
       <c r="N332" s="3"/>
       <c r="O332" s="3"/>
     </row>
-    <row r="333" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A333" s="3" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C333" s="3">
         <v>332</v>
@@ -13326,76 +13345,76 @@
         <v>0</v>
       </c>
       <c r="G333" s="3" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H333" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="I333" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J333" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="K333" s="3" t="s">
         <v>695</v>
       </c>
-      <c r="K333" s="3" t="s">
-        <v>697</v>
-      </c>
       <c r="L333" s="3">
         <v>1</v>
       </c>
       <c r="M333" s="3" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="N333" s="3"/>
       <c r="O333" s="3"/>
     </row>
-    <row r="334" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A334" s="6" t="s">
-        <v>626</v>
-      </c>
-      <c r="B334" s="6" t="s">
-        <v>636</v>
-      </c>
-      <c r="C334" s="6">
+    <row r="334" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A334" s="5" t="s">
+        <v>625</v>
+      </c>
+      <c r="B334" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="C334" s="5">
         <v>333</v>
       </c>
-      <c r="D334" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E334" s="6"/>
-      <c r="F334" s="6">
-        <v>0</v>
-      </c>
-      <c r="G334" s="6" t="s">
+      <c r="D334" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E334" s="5"/>
+      <c r="F334" s="5">
+        <v>0</v>
+      </c>
+      <c r="G334" s="5" t="s">
+        <v>640</v>
+      </c>
+      <c r="H334" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="H334" s="6" t="s">
+      <c r="I334" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J334" s="5" t="s">
+        <v>693</v>
+      </c>
+      <c r="K334" s="5" t="s">
+        <v>696</v>
+      </c>
+      <c r="L334" s="5">
+        <v>2</v>
+      </c>
+      <c r="M334" s="5" t="s">
+        <v>638</v>
+      </c>
+      <c r="N334" s="5"/>
+      <c r="O334" s="5"/>
+    </row>
+    <row r="335" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A335" s="3" t="s">
         <v>642</v>
       </c>
-      <c r="I334" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="J334" s="6" t="s">
-        <v>695</v>
-      </c>
-      <c r="K334" s="6" t="s">
-        <v>698</v>
-      </c>
-      <c r="L334" s="6">
-        <v>2</v>
-      </c>
-      <c r="M334" s="6" t="s">
-        <v>639</v>
-      </c>
-      <c r="N334" s="6"/>
-      <c r="O334" s="6"/>
-    </row>
-    <row r="335" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A335" s="3" t="s">
+      <c r="B335" s="3" t="s">
         <v>643</v>
-      </c>
-      <c r="B335" s="3" t="s">
-        <v>644</v>
       </c>
       <c r="C335" s="3">
         <v>334</v>
@@ -13408,19 +13427,19 @@
         <v>0</v>
       </c>
       <c r="G335" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="H335" s="3" t="s">
         <v>645</v>
       </c>
-      <c r="H335" s="3" t="s">
-        <v>646</v>
-      </c>
       <c r="I335" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J335" s="3" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="K335" s="3" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="L335" s="3">
         <v>2</v>
@@ -13431,12 +13450,12 @@
       <c r="N335" s="3"/>
       <c r="O335" s="3"/>
     </row>
-    <row r="336" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
+        <v>642</v>
+      </c>
+      <c r="B336" t="s">
         <v>643</v>
-      </c>
-      <c r="B336" t="s">
-        <v>644</v>
       </c>
       <c r="C336">
         <v>335</v>
@@ -13448,62 +13467,62 @@
         <v>0</v>
       </c>
       <c r="G336" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H336" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="I336" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="337" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A337" s="5" t="s">
+    <row r="337" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A337" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="B337" s="4" t="s">
         <v>643</v>
       </c>
-      <c r="B337" s="5" t="s">
-        <v>644</v>
-      </c>
-      <c r="C337" s="5">
+      <c r="C337" s="4">
         <v>336</v>
       </c>
-      <c r="D337" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E337" s="5"/>
-      <c r="F337" s="5">
-        <v>0</v>
-      </c>
-      <c r="G337" s="5" t="s">
-        <v>648</v>
-      </c>
-      <c r="H337" s="5" t="s">
-        <v>646</v>
-      </c>
-      <c r="I337" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J337" s="5" t="s">
-        <v>695</v>
-      </c>
-      <c r="K337" s="5" t="s">
-        <v>737</v>
-      </c>
-      <c r="L337" s="5">
+      <c r="D337" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E337" s="4"/>
+      <c r="F337" s="4">
+        <v>0</v>
+      </c>
+      <c r="G337" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="H337" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="I337" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J337" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="K337" s="4" t="s">
+        <v>735</v>
+      </c>
+      <c r="L337" s="4">
         <v>2</v>
       </c>
-      <c r="M337" s="5" t="s">
+      <c r="M337" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="N337" s="5"/>
-      <c r="O337" s="5"/>
-    </row>
-    <row r="338" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="N337" s="4"/>
+      <c r="O337" s="4"/>
+    </row>
+    <row r="338" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
+        <v>642</v>
+      </c>
+      <c r="B338" t="s">
         <v>643</v>
-      </c>
-      <c r="B338" t="s">
-        <v>644</v>
       </c>
       <c r="C338">
         <v>337</v>
@@ -13515,103 +13534,103 @@
         <v>0</v>
       </c>
       <c r="G338" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H338" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="I338" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="339" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A339" s="7" t="s">
+    <row r="339" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A339" s="6" t="s">
+        <v>642</v>
+      </c>
+      <c r="B339" s="6" t="s">
         <v>643</v>
       </c>
-      <c r="B339" s="7" t="s">
-        <v>644</v>
-      </c>
-      <c r="C339" s="7">
+      <c r="C339" s="6">
         <v>338</v>
       </c>
-      <c r="D339" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E339" s="7"/>
-      <c r="F339" s="7">
-        <v>0</v>
-      </c>
-      <c r="G339" s="7" t="s">
+      <c r="D339" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E339" s="6"/>
+      <c r="F339" s="6">
+        <v>0</v>
+      </c>
+      <c r="G339" s="6" t="s">
+        <v>649</v>
+      </c>
+      <c r="H339" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="I339" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J339" s="6" t="s">
+        <v>693</v>
+      </c>
+      <c r="K339" s="6" t="s">
+        <v>704</v>
+      </c>
+      <c r="L339" s="6">
+        <v>1</v>
+      </c>
+      <c r="M339" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N339" s="6"/>
+      <c r="O339" s="6"/>
+    </row>
+    <row r="340" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A340" s="6" t="s">
+        <v>642</v>
+      </c>
+      <c r="B340" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="C340" s="6">
+        <v>339</v>
+      </c>
+      <c r="D340" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E340" s="6"/>
+      <c r="F340" s="6">
+        <v>0</v>
+      </c>
+      <c r="G340" s="6" t="s">
         <v>650</v>
       </c>
-      <c r="H339" s="7" t="s">
-        <v>646</v>
-      </c>
-      <c r="I339" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="J339" s="7" t="s">
-        <v>695</v>
-      </c>
-      <c r="K339" s="7" t="s">
-        <v>706</v>
-      </c>
-      <c r="L339" s="7">
-        <v>1</v>
-      </c>
-      <c r="M339" s="7" t="s">
+      <c r="H340" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="I340" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J340" s="6" t="s">
+        <v>693</v>
+      </c>
+      <c r="K340" s="6" t="s">
+        <v>703</v>
+      </c>
+      <c r="L340" s="6">
+        <v>1</v>
+      </c>
+      <c r="M340" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="N339" s="7"/>
-      <c r="O339" s="7"/>
-    </row>
-    <row r="340" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A340" s="7" t="s">
-        <v>643</v>
-      </c>
-      <c r="B340" s="7" t="s">
-        <v>644</v>
-      </c>
-      <c r="C340" s="7">
-        <v>339</v>
-      </c>
-      <c r="D340" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E340" s="7"/>
-      <c r="F340" s="7">
-        <v>0</v>
-      </c>
-      <c r="G340" s="7" t="s">
+      <c r="N340" s="6"/>
+      <c r="O340" s="6"/>
+    </row>
+    <row r="341" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>642</v>
+      </c>
+      <c r="B341" t="s">
         <v>651</v>
-      </c>
-      <c r="H340" s="7" t="s">
-        <v>646</v>
-      </c>
-      <c r="I340" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J340" s="7" t="s">
-        <v>695</v>
-      </c>
-      <c r="K340" s="7" t="s">
-        <v>705</v>
-      </c>
-      <c r="L340" s="7">
-        <v>1</v>
-      </c>
-      <c r="M340" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N340" s="7"/>
-      <c r="O340" s="7"/>
-    </row>
-    <row r="341" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A341" t="s">
-        <v>643</v>
-      </c>
-      <c r="B341" t="s">
-        <v>652</v>
       </c>
       <c r="C341">
         <v>340</v>
@@ -13623,21 +13642,21 @@
         <v>1</v>
       </c>
       <c r="G341" t="s">
+        <v>652</v>
+      </c>
+      <c r="H341" t="s">
         <v>653</v>
-      </c>
-      <c r="H341" t="s">
-        <v>654</v>
       </c>
       <c r="I341" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="342" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B342" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C342">
         <v>341</v>
@@ -13649,21 +13668,21 @@
         <v>1</v>
       </c>
       <c r="G342" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H342" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="I342" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="343" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A343" s="3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C343" s="3">
         <v>342</v>
@@ -13676,7 +13695,7 @@
         <v>0</v>
       </c>
       <c r="G343" s="3" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H343" s="3" t="s">
         <v>166</v>
@@ -13685,10 +13704,10 @@
         <v>17</v>
       </c>
       <c r="J343" s="3" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="K343" s="3" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="L343" s="3">
         <v>2</v>
@@ -13699,12 +13718,12 @@
       <c r="N343" s="3"/>
       <c r="O343" s="3"/>
     </row>
-    <row r="344" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B344" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C344">
         <v>343</v>
@@ -13716,21 +13735,21 @@
         <v>1</v>
       </c>
       <c r="G344" t="s">
+        <v>656</v>
+      </c>
+      <c r="H344" t="s">
         <v>657</v>
       </c>
-      <c r="H344" t="s">
-        <v>658</v>
-      </c>
       <c r="I344" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="345" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B345" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C345">
         <v>344</v>
@@ -13742,62 +13761,62 @@
         <v>1</v>
       </c>
       <c r="G345" t="s">
+        <v>658</v>
+      </c>
+      <c r="H345" t="s">
         <v>659</v>
       </c>
-      <c r="H345" t="s">
+      <c r="I345" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="346" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A346" s="7" t="s">
+        <v>642</v>
+      </c>
+      <c r="B346" s="7" t="s">
+        <v>651</v>
+      </c>
+      <c r="C346" s="7">
+        <v>345</v>
+      </c>
+      <c r="D346" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E346" s="7"/>
+      <c r="F346" s="7">
+        <v>0</v>
+      </c>
+      <c r="G346" s="7" t="s">
         <v>660</v>
       </c>
-      <c r="I345" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="346" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A346" s="8" t="s">
-        <v>643</v>
-      </c>
-      <c r="B346" s="8" t="s">
-        <v>652</v>
-      </c>
-      <c r="C346" s="8">
-        <v>345</v>
-      </c>
-      <c r="D346" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E346" s="8"/>
-      <c r="F346" s="8">
-        <v>0</v>
-      </c>
-      <c r="G346" s="8" t="s">
-        <v>661</v>
-      </c>
-      <c r="H346" s="8" t="s">
-        <v>656</v>
-      </c>
-      <c r="I346" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="J346" s="8" t="s">
-        <v>695</v>
-      </c>
-      <c r="K346" s="8" t="s">
-        <v>707</v>
-      </c>
-      <c r="L346" s="8">
-        <v>1</v>
-      </c>
-      <c r="M346" s="8" t="s">
+      <c r="H346" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="I346" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J346" s="7" t="s">
+        <v>693</v>
+      </c>
+      <c r="K346" s="7" t="s">
+        <v>705</v>
+      </c>
+      <c r="L346" s="7">
+        <v>1</v>
+      </c>
+      <c r="M346" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="N346" s="8"/>
-      <c r="O346" s="8"/>
-    </row>
-    <row r="347" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="N346" s="7"/>
+      <c r="O346" s="7"/>
+    </row>
+    <row r="347" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A347" s="3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C347" s="3">
         <v>346</v>
@@ -13810,19 +13829,19 @@
         <v>0</v>
       </c>
       <c r="G347" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="H347" s="3" t="s">
         <v>662</v>
       </c>
-      <c r="H347" s="3" t="s">
-        <v>663</v>
-      </c>
       <c r="I347" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J347" s="3" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="K347" s="3" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="L347" s="3">
         <v>1</v>
@@ -13848,6 +13867,7 @@
     </filterColumn>
     <filterColumn colId="9">
       <filters>
+        <filter val="1"/>
         <filter val="tad-1"/>
       </filters>
     </filterColumn>
